--- a/output/full_scan/batch_seq6_2026-08-24.xlsx
+++ b/output/full_scan/batch_seq6_2026-08-24.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O117"/>
+  <dimension ref="A1:O118"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -1269,21 +1269,21 @@
     </row>
     <row r="16">
       <c r="A16" s="2" t="n">
-        <v>6279</v>
+        <v>6225</v>
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>胡連</t>
+          <t>天瀚</t>
         </is>
       </c>
       <c r="C16" s="2" t="n">
         <v/>
       </c>
       <c r="D16" s="2" t="n">
-        <v>556.97994557398</v>
+        <v>565.2665687518955</v>
       </c>
       <c r="E16" s="2" t="n">
-        <v>126.5</v>
+        <v>71.09999999999999</v>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
@@ -1294,13 +1294,13 @@
         <v>0</v>
       </c>
       <c r="H16" s="2" t="n">
-        <v>57.32930090818452</v>
+        <v>94.38567322331301</v>
       </c>
       <c r="I16" s="2" t="n">
-        <v>19.75787255245362</v>
+        <v>44.62060085491891</v>
       </c>
       <c r="J16" s="2" t="n">
-        <v>0.3096781294966684</v>
+        <v>0.6266568751895578</v>
       </c>
       <c r="K16" s="2" t="n">
         <v>0</v>
@@ -1312,31 +1312,31 @@
         <v>-1</v>
       </c>
       <c r="N16" s="2" t="n">
-        <v>0.1350312344102766</v>
+        <v>4.141969838713514</v>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, rsi_strong, breakout_20d, market_above_ma60, adx_trending, stronger_than_market, obv_uptrend, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="n">
-        <v>6183</v>
+        <v>6279</v>
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>關貿</t>
+          <t>胡連</t>
         </is>
       </c>
       <c r="C17" s="2" t="n">
         <v/>
       </c>
       <c r="D17" s="2" t="n">
-        <v>551.1015347083878</v>
+        <v>556.97994557398</v>
       </c>
       <c r="E17" s="2" t="n">
-        <v>93.5</v>
+        <v>126.5</v>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
@@ -1347,13 +1347,13 @@
         <v>0</v>
       </c>
       <c r="H17" s="2" t="n">
-        <v>56.35654500065407</v>
+        <v>57.32930090818452</v>
       </c>
       <c r="I17" s="2" t="n">
-        <v>34.35946189940574</v>
+        <v>19.75787255245362</v>
       </c>
       <c r="J17" s="2" t="n">
-        <v>0.4391858539100293</v>
+        <v>0.3096781294966684</v>
       </c>
       <c r="K17" s="2" t="n">
         <v>0</v>
@@ -1365,31 +1365,31 @@
         <v>-1</v>
       </c>
       <c r="N17" s="2" t="n">
-        <v>-0.0067474353005078</v>
+        <v>0.1350312344102766</v>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>rsi_strong, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="n">
-        <v>6292</v>
+        <v>6183</v>
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>迅德</t>
+          <t>關貿</t>
         </is>
       </c>
       <c r="C18" s="2" t="n">
         <v/>
       </c>
       <c r="D18" s="2" t="n">
-        <v>544.1622320299281</v>
+        <v>551.1015347083878</v>
       </c>
       <c r="E18" s="2" t="n">
-        <v>61.2</v>
+        <v>93.5</v>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
@@ -1400,13 +1400,13 @@
         <v>0</v>
       </c>
       <c r="H18" s="2" t="n">
-        <v>54.49226623727488</v>
+        <v>56.35654500065407</v>
       </c>
       <c r="I18" s="2" t="n">
-        <v>25.23202864473241</v>
+        <v>34.35946189940574</v>
       </c>
       <c r="J18" s="2" t="n">
-        <v>0.269006557328703</v>
+        <v>0.4391858539100293</v>
       </c>
       <c r="K18" s="2" t="n">
         <v>0</v>
@@ -1418,31 +1418,31 @@
         <v>-1</v>
       </c>
       <c r="N18" s="2" t="n">
-        <v>0.06447241992789871</v>
+        <v>-0.0067474353005078</v>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>rsi_strong, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="n">
-        <v>6472</v>
+        <v>6292</v>
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>保瑞</t>
+          <t>迅德</t>
         </is>
       </c>
       <c r="C19" s="2" t="n">
         <v/>
       </c>
       <c r="D19" s="2" t="n">
-        <v>539.3710949614707</v>
+        <v>544.1622320299281</v>
       </c>
       <c r="E19" s="2" t="n">
-        <v>453</v>
+        <v>61.2</v>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
@@ -1453,13 +1453,13 @@
         <v>0</v>
       </c>
       <c r="H19" s="2" t="n">
-        <v>63.33805398620923</v>
+        <v>54.49226623727488</v>
       </c>
       <c r="I19" s="2" t="n">
-        <v>26.76521084706964</v>
+        <v>25.23202864473241</v>
       </c>
       <c r="J19" s="2" t="n">
-        <v>2.049279003312116</v>
+        <v>0.269006557328703</v>
       </c>
       <c r="K19" s="2" t="n">
         <v>0</v>
@@ -1471,31 +1471,31 @@
         <v>-1</v>
       </c>
       <c r="N19" s="2" t="n">
-        <v>4.574003856211238</v>
+        <v>0.06447241992789871</v>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>volume_break, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="n">
-        <v>6277</v>
+        <v>6472</v>
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>宏正</t>
+          <t>保瑞</t>
         </is>
       </c>
       <c r="C20" s="2" t="n">
         <v/>
       </c>
       <c r="D20" s="2" t="n">
-        <v>521.7311181458014</v>
+        <v>539.3710949614707</v>
       </c>
       <c r="E20" s="2" t="n">
-        <v>81.2</v>
+        <v>453</v>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
@@ -1506,13 +1506,13 @@
         <v>0</v>
       </c>
       <c r="H20" s="2" t="n">
-        <v>53.69637355335114</v>
+        <v>63.33805398620923</v>
       </c>
       <c r="I20" s="2" t="n">
-        <v>41.85617117978285</v>
+        <v>26.76521084706964</v>
       </c>
       <c r="J20" s="2" t="n">
-        <v>0.4650145341585063</v>
+        <v>2.049279003312116</v>
       </c>
       <c r="K20" s="2" t="n">
         <v>0</v>
@@ -1524,31 +1524,31 @@
         <v>-1</v>
       </c>
       <c r="N20" s="2" t="n">
-        <v>-0.127914710025073</v>
+        <v>4.574003856211238</v>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, mfi_strong, above_ichimoku_cloud</t>
+          <t>volume_break, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="n">
-        <v>6173</v>
+        <v>6277</v>
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>信昌電</t>
+          <t>宏正</t>
         </is>
       </c>
       <c r="C21" s="2" t="n">
         <v/>
       </c>
       <c r="D21" s="2" t="n">
-        <v>521.5513776421594</v>
+        <v>521.7311181458014</v>
       </c>
       <c r="E21" s="2" t="n">
-        <v>203</v>
+        <v>81.2</v>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
@@ -1559,13 +1559,13 @@
         <v>0</v>
       </c>
       <c r="H21" s="2" t="n">
-        <v>50.70764770709623</v>
+        <v>53.69637355335114</v>
       </c>
       <c r="I21" s="2" t="n">
-        <v>21.31846900263826</v>
+        <v>41.85617117978285</v>
       </c>
       <c r="J21" s="2" t="n">
-        <v>0.6830850719485936</v>
+        <v>0.4650145341585063</v>
       </c>
       <c r="K21" s="2" t="n">
         <v>0</v>
@@ -1577,31 +1577,31 @@
         <v>-1</v>
       </c>
       <c r="N21" s="2" t="n">
-        <v>6.082854515648639</v>
+        <v>-0.127914710025073</v>
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="n">
-        <v>6449</v>
+        <v>6173</v>
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>鈺邦</t>
+          <t>信昌電</t>
         </is>
       </c>
       <c r="C22" s="2" t="n">
         <v/>
       </c>
       <c r="D22" s="2" t="n">
-        <v>517.872762658457</v>
+        <v>521.5513776421594</v>
       </c>
       <c r="E22" s="2" t="n">
-        <v>210.5</v>
+        <v>203</v>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
@@ -1612,13 +1612,13 @@
         <v>0</v>
       </c>
       <c r="H22" s="2" t="n">
-        <v>36.93276573158496</v>
+        <v>50.70764770709623</v>
       </c>
       <c r="I22" s="2" t="n">
-        <v>28.116758428097</v>
+        <v>21.31846900263826</v>
       </c>
       <c r="J22" s="2" t="n">
-        <v>0.2760620709266338</v>
+        <v>0.6830850719485936</v>
       </c>
       <c r="K22" s="2" t="n">
         <v>0</v>
@@ -1630,7 +1630,7 @@
         <v>-1</v>
       </c>
       <c r="N22" s="2" t="n">
-        <v>1.616541324871672</v>
+        <v>6.082854515648639</v>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
@@ -1640,21 +1640,21 @@
     </row>
     <row r="23">
       <c r="A23" s="2" t="n">
-        <v>6416</v>
+        <v>6449</v>
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>瑞祺電通</t>
+          <t>鈺邦</t>
         </is>
       </c>
       <c r="C23" s="2" t="n">
         <v/>
       </c>
       <c r="D23" s="2" t="n">
-        <v>509.1221018412084</v>
+        <v>517.872762658457</v>
       </c>
       <c r="E23" s="2" t="n">
-        <v>99</v>
+        <v>210.5</v>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
@@ -1665,13 +1665,13 @@
         <v>0</v>
       </c>
       <c r="H23" s="2" t="n">
-        <v>53.13519133321768</v>
+        <v>36.93276573158496</v>
       </c>
       <c r="I23" s="2" t="n">
-        <v>16.57547768170344</v>
+        <v>28.116758428097</v>
       </c>
       <c r="J23" s="2" t="n">
-        <v>0.5420470582911915</v>
+        <v>0.2760620709266338</v>
       </c>
       <c r="K23" s="2" t="n">
         <v>0</v>
@@ -1683,31 +1683,31 @@
         <v>-1</v>
       </c>
       <c r="N23" s="2" t="n">
-        <v>-0.1203000696575484</v>
+        <v>1.616541324871672</v>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="n">
-        <v>6464</v>
+        <v>6416</v>
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>台數科</t>
+          <t>瑞祺電通</t>
         </is>
       </c>
       <c r="C24" s="2" t="n">
         <v/>
       </c>
       <c r="D24" s="2" t="n">
-        <v>506.3833980125215</v>
+        <v>509.1221018412084</v>
       </c>
       <c r="E24" s="2" t="n">
-        <v>79</v>
+        <v>99</v>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
@@ -1718,13 +1718,13 @@
         <v>0</v>
       </c>
       <c r="H24" s="2" t="n">
-        <v>54.87309752538389</v>
+        <v>53.13519133321768</v>
       </c>
       <c r="I24" s="2" t="n">
-        <v>28.69702390485501</v>
+        <v>16.57547768170344</v>
       </c>
       <c r="J24" s="2" t="n">
-        <v>0.3508607660460058</v>
+        <v>0.5420470582911915</v>
       </c>
       <c r="K24" s="2" t="n">
         <v>0</v>
@@ -1736,31 +1736,31 @@
         <v>-1</v>
       </c>
       <c r="N24" s="2" t="n">
-        <v>0.1407133671833669</v>
+        <v>-0.1203000696575484</v>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="n">
-        <v>6187</v>
+        <v>6464</v>
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>萬潤</t>
+          <t>台數科</t>
         </is>
       </c>
       <c r="C25" s="2" t="n">
         <v/>
       </c>
       <c r="D25" s="2" t="n">
-        <v>502.3283466811541</v>
+        <v>506.3833980125215</v>
       </c>
       <c r="E25" s="2" t="n">
-        <v>1205</v>
+        <v>79</v>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
@@ -1771,13 +1771,13 @@
         <v>0</v>
       </c>
       <c r="H25" s="2" t="n">
-        <v>53.84090460690073</v>
+        <v>54.87309752538389</v>
       </c>
       <c r="I25" s="2" t="n">
-        <v>19.82961838984092</v>
+        <v>28.69702390485501</v>
       </c>
       <c r="J25" s="2" t="n">
-        <v>0.4099838167857204</v>
+        <v>0.3508607660460058</v>
       </c>
       <c r="K25" s="2" t="n">
         <v>0</v>
@@ -1789,31 +1789,31 @@
         <v>-1</v>
       </c>
       <c r="N25" s="2" t="n">
-        <v>7.742547560870449</v>
+        <v>0.1407133671833669</v>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="n">
-        <v>6245</v>
+        <v>6187</v>
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>立端</t>
+          <t>萬潤</t>
         </is>
       </c>
       <c r="C26" s="2" t="n">
         <v/>
       </c>
       <c r="D26" s="2" t="n">
-        <v>502.1146596167421</v>
+        <v>502.3283466811541</v>
       </c>
       <c r="E26" s="2" t="n">
-        <v>81.59999999999999</v>
+        <v>1205</v>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
@@ -1824,13 +1824,13 @@
         <v>0</v>
       </c>
       <c r="H26" s="2" t="n">
-        <v>48.08474472977267</v>
+        <v>53.84090460690073</v>
       </c>
       <c r="I26" s="2" t="n">
-        <v>12.95884067215067</v>
+        <v>19.82961838984092</v>
       </c>
       <c r="J26" s="2" t="n">
-        <v>0.3402064504765876</v>
+        <v>0.4099838167857204</v>
       </c>
       <c r="K26" s="2" t="n">
         <v>0</v>
@@ -1842,31 +1842,31 @@
         <v>-1</v>
       </c>
       <c r="N26" s="2" t="n">
-        <v>-0.325579527139902</v>
+        <v>7.742547560870449</v>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="n">
-        <v>6474</v>
+        <v>6245</v>
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>華豫寧</t>
+          <t>立端</t>
         </is>
       </c>
       <c r="C27" s="2" t="n">
         <v/>
       </c>
       <c r="D27" s="2" t="n">
-        <v>481.7297475998201</v>
+        <v>502.1146596167421</v>
       </c>
       <c r="E27" s="2" t="n">
-        <v>39</v>
+        <v>81.59999999999999</v>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
@@ -1877,13 +1877,13 @@
         <v>0</v>
       </c>
       <c r="H27" s="2" t="n">
-        <v>54.99053647187008</v>
+        <v>48.08474472977267</v>
       </c>
       <c r="I27" s="2" t="n">
-        <v>14.25275737848979</v>
+        <v>12.95884067215067</v>
       </c>
       <c r="J27" s="2" t="n">
-        <v>1.23346002423511</v>
+        <v>0.3402064504765876</v>
       </c>
       <c r="K27" s="2" t="n">
         <v>0</v>
@@ -1895,31 +1895,31 @@
         <v>-1</v>
       </c>
       <c r="N27" s="2" t="n">
-        <v>0.0413774894191045</v>
+        <v>-0.325579527139902</v>
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="n">
-        <v>6164</v>
+        <v>6474</v>
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>華興</t>
+          <t>華豫寧</t>
         </is>
       </c>
       <c r="C28" s="2" t="n">
         <v/>
       </c>
       <c r="D28" s="2" t="n">
-        <v>451.5791911140613</v>
+        <v>481.7297475998201</v>
       </c>
       <c r="E28" s="2" t="n">
-        <v>12</v>
+        <v>39</v>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
@@ -1930,13 +1930,13 @@
         <v>0</v>
       </c>
       <c r="H28" s="2" t="n">
-        <v>47.47561984680894</v>
+        <v>54.99053647187008</v>
       </c>
       <c r="I28" s="2" t="n">
-        <v>24.86801990149193</v>
+        <v>14.25275737848979</v>
       </c>
       <c r="J28" s="2" t="n">
-        <v>0.6315481263037775</v>
+        <v>1.23346002423511</v>
       </c>
       <c r="K28" s="2" t="n">
         <v>0</v>
@@ -1948,31 +1948,31 @@
         <v>-1</v>
       </c>
       <c r="N28" s="2" t="n">
-        <v>0.09034966624974369</v>
+        <v>0.0413774894191045</v>
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="n">
-        <v>6190</v>
+        <v>6164</v>
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>萬泰科</t>
+          <t>華興</t>
         </is>
       </c>
       <c r="C29" s="2" t="n">
         <v/>
       </c>
       <c r="D29" s="2" t="n">
-        <v>447.8566960279865</v>
+        <v>451.5791911140613</v>
       </c>
       <c r="E29" s="2" t="n">
-        <v>65</v>
+        <v>12</v>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
@@ -1983,13 +1983,13 @@
         <v>0</v>
       </c>
       <c r="H29" s="2" t="n">
-        <v>41.16293509904949</v>
+        <v>47.47561984680894</v>
       </c>
       <c r="I29" s="2" t="n">
-        <v>29.0186793067664</v>
+        <v>24.86801990149193</v>
       </c>
       <c r="J29" s="2" t="n">
-        <v>0.978913158198054</v>
+        <v>0.6315481263037775</v>
       </c>
       <c r="K29" s="2" t="n">
         <v>0</v>
@@ -2001,31 +2001,31 @@
         <v>-1</v>
       </c>
       <c r="N29" s="2" t="n">
-        <v>0.3045585351141624</v>
+        <v>0.09034966624974369</v>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="n">
-        <v>6278</v>
+        <v>6190</v>
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>台表科</t>
+          <t>萬泰科</t>
         </is>
       </c>
       <c r="C30" s="2" t="n">
         <v/>
       </c>
       <c r="D30" s="2" t="n">
-        <v>445.8765763168881</v>
+        <v>447.8566960279865</v>
       </c>
       <c r="E30" s="2" t="n">
-        <v>179</v>
+        <v>65</v>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
@@ -2036,13 +2036,13 @@
         <v>0</v>
       </c>
       <c r="H30" s="2" t="n">
-        <v>54.5908988217746</v>
+        <v>41.16293509904949</v>
       </c>
       <c r="I30" s="2" t="n">
-        <v>17.49126158556047</v>
+        <v>29.0186793067664</v>
       </c>
       <c r="J30" s="2" t="n">
-        <v>1.421167927261905</v>
+        <v>0.978913158198054</v>
       </c>
       <c r="K30" s="2" t="n">
         <v>0</v>
@@ -2054,31 +2054,31 @@
         <v>-1</v>
       </c>
       <c r="N30" s="2" t="n">
-        <v>3.547685689266947</v>
+        <v>0.3045585351141624</v>
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="n">
-        <v>6271</v>
+        <v>6278</v>
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>同欣電</t>
+          <t>台表科</t>
         </is>
       </c>
       <c r="C31" s="2" t="n">
         <v/>
       </c>
       <c r="D31" s="2" t="n">
-        <v>436.1246534310922</v>
+        <v>445.8765763168881</v>
       </c>
       <c r="E31" s="2" t="n">
-        <v>193</v>
+        <v>179</v>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
@@ -2089,13 +2089,13 @@
         <v>0</v>
       </c>
       <c r="H31" s="2" t="n">
-        <v>46.98723495782254</v>
+        <v>54.5908988217746</v>
       </c>
       <c r="I31" s="2" t="n">
-        <v>15.76966316391111</v>
+        <v>17.49126158556047</v>
       </c>
       <c r="J31" s="2" t="n">
-        <v>0.3276568243796372</v>
+        <v>1.421167927261905</v>
       </c>
       <c r="K31" s="2" t="n">
         <v>0</v>
@@ -2107,7 +2107,7 @@
         <v>-1</v>
       </c>
       <c r="N31" s="2" t="n">
-        <v>2.415297272841414</v>
+        <v>3.547685689266947</v>
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
@@ -2117,21 +2117,21 @@
     </row>
     <row r="32">
       <c r="A32" s="2" t="n">
-        <v>6291</v>
+        <v>6271</v>
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>沛亨</t>
+          <t>同欣電</t>
         </is>
       </c>
       <c r="C32" s="2" t="n">
         <v/>
       </c>
       <c r="D32" s="2" t="n">
-        <v>425.4243030395256</v>
+        <v>436.1246534310922</v>
       </c>
       <c r="E32" s="2" t="n">
-        <v>366</v>
+        <v>193</v>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
@@ -2142,13 +2142,13 @@
         <v>0</v>
       </c>
       <c r="H32" s="2" t="n">
-        <v>43.80294612670204</v>
+        <v>46.98723495782254</v>
       </c>
       <c r="I32" s="2" t="n">
-        <v>18.54624026064787</v>
+        <v>15.76966316391111</v>
       </c>
       <c r="J32" s="2" t="n">
-        <v>0.8681656001415158</v>
+        <v>0.3276568243796372</v>
       </c>
       <c r="K32" s="2" t="n">
         <v>0</v>
@@ -2160,7 +2160,7 @@
         <v>-1</v>
       </c>
       <c r="N32" s="2" t="n">
-        <v>5.568758779221099</v>
+        <v>2.415297272841414</v>
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
@@ -2170,21 +2170,21 @@
     </row>
     <row r="33">
       <c r="A33" s="2" t="n">
-        <v>6405</v>
+        <v>6291</v>
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>悅城</t>
+          <t>沛亨</t>
         </is>
       </c>
       <c r="C33" s="2" t="n">
         <v/>
       </c>
       <c r="D33" s="2" t="n">
-        <v>422.6352572653119</v>
+        <v>425.4243030395256</v>
       </c>
       <c r="E33" s="2" t="n">
-        <v>38.15</v>
+        <v>366</v>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
@@ -2195,13 +2195,13 @@
         <v>0</v>
       </c>
       <c r="H33" s="2" t="n">
-        <v>37.74481237508036</v>
+        <v>43.80294612670204</v>
       </c>
       <c r="I33" s="2" t="n">
-        <v>27.69350223929319</v>
+        <v>18.54624026064787</v>
       </c>
       <c r="J33" s="2" t="n">
-        <v>0.6709462592342638</v>
+        <v>0.8681656001415158</v>
       </c>
       <c r="K33" s="2" t="n">
         <v>0</v>
@@ -2213,31 +2213,31 @@
         <v>-1</v>
       </c>
       <c r="N33" s="2" t="n">
-        <v>0.7482694232097629</v>
+        <v>5.568758779221099</v>
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="n">
-        <v>6175</v>
+        <v>6405</v>
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>立敦</t>
+          <t>悅城</t>
         </is>
       </c>
       <c r="C34" s="2" t="n">
         <v/>
       </c>
       <c r="D34" s="2" t="n">
-        <v>418.5441263676134</v>
+        <v>422.6352572653119</v>
       </c>
       <c r="E34" s="2" t="n">
-        <v>73.2</v>
+        <v>38.15</v>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
@@ -2248,13 +2248,13 @@
         <v>0</v>
       </c>
       <c r="H34" s="2" t="n">
-        <v>37.73882543606933</v>
+        <v>37.74481237508036</v>
       </c>
       <c r="I34" s="2" t="n">
-        <v>19.71299358466462</v>
+        <v>27.69350223929319</v>
       </c>
       <c r="J34" s="2" t="n">
-        <v>0.275314071946272</v>
+        <v>0.6709462592342638</v>
       </c>
       <c r="K34" s="2" t="n">
         <v>0</v>
@@ -2266,31 +2266,31 @@
         <v>-1</v>
       </c>
       <c r="N34" s="2" t="n">
-        <v>0.6506399202478663</v>
+        <v>0.7482694232097629</v>
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="n">
-        <v>6409</v>
+        <v>6175</v>
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>旭隼</t>
+          <t>立敦</t>
         </is>
       </c>
       <c r="C35" s="2" t="n">
         <v/>
       </c>
       <c r="D35" s="2" t="n">
-        <v>415.0249874016182</v>
+        <v>418.5441263676134</v>
       </c>
       <c r="E35" s="2" t="n">
-        <v>1010</v>
+        <v>73.2</v>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
@@ -2301,13 +2301,13 @@
         <v>0</v>
       </c>
       <c r="H35" s="2" t="n">
-        <v>51.03618321968388</v>
+        <v>37.73882543606933</v>
       </c>
       <c r="I35" s="2" t="n">
-        <v>17.81070301245841</v>
+        <v>19.71299358466462</v>
       </c>
       <c r="J35" s="2" t="n">
-        <v>0.3730118919780305</v>
+        <v>0.275314071946272</v>
       </c>
       <c r="K35" s="2" t="n">
         <v>0</v>
@@ -2319,7 +2319,7 @@
         <v>-1</v>
       </c>
       <c r="N35" s="2" t="n">
-        <v>2.48016758773413</v>
+        <v>0.6506399202478663</v>
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
@@ -2329,21 +2329,21 @@
     </row>
     <row r="36">
       <c r="A36" s="2" t="n">
-        <v>6261</v>
+        <v>6409</v>
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>久元</t>
+          <t>旭隼</t>
         </is>
       </c>
       <c r="C36" s="2" t="n">
         <v/>
       </c>
       <c r="D36" s="2" t="n">
-        <v>414.2461143328666</v>
+        <v>415.0249874016182</v>
       </c>
       <c r="E36" s="2" t="n">
-        <v>78.59999999999999</v>
+        <v>1010</v>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
@@ -2354,13 +2354,13 @@
         <v>0</v>
       </c>
       <c r="H36" s="2" t="n">
-        <v>44.98326197227701</v>
+        <v>51.03618321968388</v>
       </c>
       <c r="I36" s="2" t="n">
-        <v>30.43279673299644</v>
+        <v>17.81070301245841</v>
       </c>
       <c r="J36" s="2" t="n">
-        <v>1.721527626305314</v>
+        <v>0.3730118919780305</v>
       </c>
       <c r="K36" s="2" t="n">
         <v>0</v>
@@ -2372,31 +2372,31 @@
         <v>-1</v>
       </c>
       <c r="N36" s="2" t="n">
-        <v>0.6940079794873855</v>
+        <v>2.48016758773413</v>
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>volume_break, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="n">
-        <v>6227</v>
+        <v>6261</v>
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>茂綸</t>
+          <t>久元</t>
         </is>
       </c>
       <c r="C37" s="2" t="n">
         <v/>
       </c>
       <c r="D37" s="2" t="n">
-        <v>411.9324542278654</v>
+        <v>414.2461143328666</v>
       </c>
       <c r="E37" s="2" t="n">
-        <v>119</v>
+        <v>78.59999999999999</v>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
@@ -2407,13 +2407,13 @@
         <v>0</v>
       </c>
       <c r="H37" s="2" t="n">
-        <v>49.0358232543802</v>
+        <v>44.98326197227701</v>
       </c>
       <c r="I37" s="2" t="n">
-        <v>12.34464542004553</v>
+        <v>30.43279673299644</v>
       </c>
       <c r="J37" s="2" t="n">
-        <v>0.5290499694296091</v>
+        <v>1.721527626305314</v>
       </c>
       <c r="K37" s="2" t="n">
         <v>0</v>
@@ -2425,31 +2425,31 @@
         <v>-1</v>
       </c>
       <c r="N37" s="2" t="n">
-        <v>-0.6267078734723113</v>
+        <v>0.6940079794873855</v>
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, mfi_strong</t>
+          <t>volume_break, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="n">
-        <v>6415</v>
+        <v>6227</v>
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>矽力*-KY</t>
+          <t>茂綸</t>
         </is>
       </c>
       <c r="C38" s="2" t="n">
         <v/>
       </c>
       <c r="D38" s="2" t="n">
-        <v>411.9177428229621</v>
+        <v>411.9324542278654</v>
       </c>
       <c r="E38" s="2" t="n">
-        <v>450</v>
+        <v>119</v>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
@@ -2460,13 +2460,13 @@
         <v>0</v>
       </c>
       <c r="H38" s="2" t="n">
-        <v>47.20781930476522</v>
+        <v>49.0358232543802</v>
       </c>
       <c r="I38" s="2" t="n">
-        <v>13.40159182184072</v>
+        <v>12.34464542004553</v>
       </c>
       <c r="J38" s="2" t="n">
-        <v>0.4116166457193171</v>
+        <v>0.5290499694296091</v>
       </c>
       <c r="K38" s="2" t="n">
         <v>0</v>
@@ -2478,7 +2478,7 @@
         <v>-1</v>
       </c>
       <c r="N38" s="2" t="n">
-        <v>4.023978723650785</v>
+        <v>-0.6267078734723113</v>
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
@@ -2488,21 +2488,21 @@
     </row>
     <row r="39">
       <c r="A39" s="2" t="n">
-        <v>6196</v>
+        <v>6415</v>
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>帆宣</t>
+          <t>矽力*-KY</t>
         </is>
       </c>
       <c r="C39" s="2" t="n">
         <v/>
       </c>
       <c r="D39" s="2" t="n">
-        <v>406.1195279949465</v>
+        <v>411.9177428229621</v>
       </c>
       <c r="E39" s="2" t="n">
-        <v>493</v>
+        <v>450</v>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
@@ -2513,13 +2513,13 @@
         <v>0</v>
       </c>
       <c r="H39" s="2" t="n">
-        <v>45.13843032745464</v>
+        <v>47.20781930476522</v>
       </c>
       <c r="I39" s="2" t="n">
-        <v>11.0484138640769</v>
+        <v>13.40159182184072</v>
       </c>
       <c r="J39" s="2" t="n">
-        <v>0.3060192570997342</v>
+        <v>0.4116166457193171</v>
       </c>
       <c r="K39" s="2" t="n">
         <v>0</v>
@@ -2531,31 +2531,31 @@
         <v>-1</v>
       </c>
       <c r="N39" s="2" t="n">
-        <v>0.3304658257203456</v>
+        <v>4.023978723650785</v>
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="n">
-        <v>6174</v>
+        <v>6196</v>
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>安碁</t>
+          <t>帆宣</t>
         </is>
       </c>
       <c r="C40" s="2" t="n">
         <v/>
       </c>
       <c r="D40" s="2" t="n">
-        <v>405.2655121349827</v>
+        <v>406.1195279949465</v>
       </c>
       <c r="E40" s="2" t="n">
-        <v>44.05</v>
+        <v>493</v>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
@@ -2566,13 +2566,13 @@
         <v>0</v>
       </c>
       <c r="H40" s="2" t="n">
-        <v>47.87279186663207</v>
+        <v>45.13843032745464</v>
       </c>
       <c r="I40" s="2" t="n">
-        <v>15.72861296487296</v>
+        <v>11.0484138640769</v>
       </c>
       <c r="J40" s="2" t="n">
-        <v>0.5205330503804975</v>
+        <v>0.3060192570997342</v>
       </c>
       <c r="K40" s="2" t="n">
         <v>0</v>
@@ -2584,31 +2584,31 @@
         <v>-1</v>
       </c>
       <c r="N40" s="2" t="n">
-        <v>0.5392786900783328</v>
+        <v>0.3304658257203456</v>
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="n">
-        <v>6207</v>
+        <v>6174</v>
       </c>
       <c r="B41" s="2" t="inlineStr">
         <is>
-          <t>雷科</t>
+          <t>安碁</t>
         </is>
       </c>
       <c r="C41" s="2" t="n">
         <v/>
       </c>
       <c r="D41" s="2" t="n">
-        <v>399.9059268362426</v>
+        <v>405.2655121349827</v>
       </c>
       <c r="E41" s="2" t="n">
-        <v>100</v>
+        <v>44.05</v>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
@@ -2619,13 +2619,13 @@
         <v>0</v>
       </c>
       <c r="H41" s="2" t="n">
-        <v>40.80362600125383</v>
+        <v>47.87279186663207</v>
       </c>
       <c r="I41" s="2" t="n">
-        <v>16.21724860520342</v>
+        <v>15.72861296487296</v>
       </c>
       <c r="J41" s="2" t="n">
-        <v>0.3382230905747763</v>
+        <v>0.5205330503804975</v>
       </c>
       <c r="K41" s="2" t="n">
         <v>0</v>
@@ -2637,7 +2637,7 @@
         <v>-1</v>
       </c>
       <c r="N41" s="2" t="n">
-        <v>0.7186502963768691</v>
+        <v>0.5392786900783328</v>
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
@@ -2647,21 +2647,21 @@
     </row>
     <row r="42">
       <c r="A42" s="2" t="n">
-        <v>6269</v>
+        <v>6207</v>
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>台郡</t>
+          <t>雷科</t>
         </is>
       </c>
       <c r="C42" s="2" t="n">
         <v/>
       </c>
       <c r="D42" s="2" t="n">
-        <v>399.2133632167949</v>
+        <v>399.9059268362426</v>
       </c>
       <c r="E42" s="2" t="n">
-        <v>61.9</v>
+        <v>100</v>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
@@ -2672,13 +2672,13 @@
         <v>0</v>
       </c>
       <c r="H42" s="2" t="n">
-        <v>49.33586725089781</v>
+        <v>40.80362600125383</v>
       </c>
       <c r="I42" s="2" t="n">
-        <v>17.45293977421679</v>
+        <v>16.21724860520342</v>
       </c>
       <c r="J42" s="2" t="n">
-        <v>0.2507405225590488</v>
+        <v>0.3382230905747763</v>
       </c>
       <c r="K42" s="2" t="n">
         <v>0</v>
@@ -2690,7 +2690,7 @@
         <v>-1</v>
       </c>
       <c r="N42" s="2" t="n">
-        <v>0.1659609936021684</v>
+        <v>0.7186502963768691</v>
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
@@ -2700,21 +2700,21 @@
     </row>
     <row r="43">
       <c r="A43" s="2" t="n">
-        <v>6465</v>
+        <v>6269</v>
       </c>
       <c r="B43" s="2" t="inlineStr">
         <is>
-          <t>威潤</t>
+          <t>台郡</t>
         </is>
       </c>
       <c r="C43" s="2" t="n">
         <v/>
       </c>
       <c r="D43" s="2" t="n">
-        <v>385.4688712048119</v>
+        <v>399.2133632167949</v>
       </c>
       <c r="E43" s="2" t="n">
-        <v>45.55</v>
+        <v>61.9</v>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
@@ -2725,13 +2725,13 @@
         <v>0</v>
       </c>
       <c r="H43" s="2" t="n">
-        <v>33.59449000640028</v>
+        <v>49.33586725089781</v>
       </c>
       <c r="I43" s="2" t="n">
-        <v>14.24832959507719</v>
+        <v>17.45293977421679</v>
       </c>
       <c r="J43" s="2" t="n">
-        <v>0.5463089947013884</v>
+        <v>0.2507405225590488</v>
       </c>
       <c r="K43" s="2" t="n">
         <v>0</v>
@@ -2743,31 +2743,31 @@
         <v>-1</v>
       </c>
       <c r="N43" s="2" t="n">
-        <v>0.2449814977342539</v>
+        <v>0.1659609936021684</v>
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="n">
-        <v>6275</v>
+        <v>6465</v>
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>元山</t>
+          <t>威潤</t>
         </is>
       </c>
       <c r="C44" s="2" t="n">
         <v/>
       </c>
       <c r="D44" s="2" t="n">
-        <v>374.5883877576902</v>
+        <v>385.4688712048119</v>
       </c>
       <c r="E44" s="2" t="n">
-        <v>44.85</v>
+        <v>45.55</v>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
@@ -2778,13 +2778,13 @@
         <v>0</v>
       </c>
       <c r="H44" s="2" t="n">
-        <v>51.86711627267249</v>
+        <v>33.59449000640028</v>
       </c>
       <c r="I44" s="2" t="n">
-        <v>18.01745090813363</v>
+        <v>14.24832959507719</v>
       </c>
       <c r="J44" s="2" t="n">
-        <v>1.344900215327147</v>
+        <v>0.5463089947013884</v>
       </c>
       <c r="K44" s="2" t="n">
         <v>0</v>
@@ -2796,31 +2796,31 @@
         <v>-1</v>
       </c>
       <c r="N44" s="2" t="n">
-        <v>0.2990890120826946</v>
+        <v>0.2449814977342539</v>
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, kd_golden_cross, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="n">
-        <v>6234</v>
+        <v>6275</v>
       </c>
       <c r="B45" s="2" t="inlineStr">
         <is>
-          <t>高僑</t>
+          <t>元山</t>
         </is>
       </c>
       <c r="C45" s="2" t="n">
         <v/>
       </c>
       <c r="D45" s="2" t="n">
-        <v>366.0849309861901</v>
+        <v>374.5883877576902</v>
       </c>
       <c r="E45" s="2" t="n">
-        <v>34.9</v>
+        <v>44.85</v>
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
@@ -2831,13 +2831,13 @@
         <v>0</v>
       </c>
       <c r="H45" s="2" t="n">
-        <v>43.96455737869568</v>
+        <v>51.86711627267249</v>
       </c>
       <c r="I45" s="2" t="n">
-        <v>22.14008439247218</v>
+        <v>18.01745090813363</v>
       </c>
       <c r="J45" s="2" t="n">
-        <v>0.2573916438798297</v>
+        <v>1.344900215327147</v>
       </c>
       <c r="K45" s="2" t="n">
         <v>0</v>
@@ -2849,31 +2849,31 @@
         <v>-1</v>
       </c>
       <c r="N45" s="2" t="n">
-        <v>0.3236478815978765</v>
+        <v>0.2990890120826946</v>
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, kd_golden_cross, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="n">
-        <v>6244</v>
+        <v>6234</v>
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t>茂迪</t>
+          <t>高僑</t>
         </is>
       </c>
       <c r="C46" s="2" t="n">
         <v/>
       </c>
       <c r="D46" s="2" t="n">
-        <v>364.0862910948558</v>
+        <v>366.0849309861901</v>
       </c>
       <c r="E46" s="2" t="n">
-        <v>24.55</v>
+        <v>34.9</v>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
@@ -2884,13 +2884,13 @@
         <v>0</v>
       </c>
       <c r="H46" s="2" t="n">
-        <v>48.09890300082114</v>
+        <v>43.96455737869568</v>
       </c>
       <c r="I46" s="2" t="n">
-        <v>18.35479216675446</v>
+        <v>22.14008439247218</v>
       </c>
       <c r="J46" s="2" t="n">
-        <v>0.721789879973309</v>
+        <v>0.2573916438798297</v>
       </c>
       <c r="K46" s="2" t="n">
         <v>0</v>
@@ -2902,31 +2902,31 @@
         <v>-1</v>
       </c>
       <c r="N46" s="2" t="n">
-        <v>0.189438935255743</v>
+        <v>0.3236478815978765</v>
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="n">
-        <v>6259</v>
+        <v>6244</v>
       </c>
       <c r="B47" s="2" t="inlineStr">
         <is>
-          <t>百徽</t>
+          <t>茂迪</t>
         </is>
       </c>
       <c r="C47" s="2" t="n">
         <v/>
       </c>
       <c r="D47" s="2" t="n">
-        <v>363.2715573028466</v>
+        <v>364.0862910948558</v>
       </c>
       <c r="E47" s="2" t="n">
-        <v>29.6</v>
+        <v>24.55</v>
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
@@ -2937,13 +2937,13 @@
         <v>0</v>
       </c>
       <c r="H47" s="2" t="n">
-        <v>43.22341216105632</v>
+        <v>48.09890300082114</v>
       </c>
       <c r="I47" s="2" t="n">
-        <v>11.52027153639223</v>
+        <v>18.35479216675446</v>
       </c>
       <c r="J47" s="2" t="n">
-        <v>0.6291044405478855</v>
+        <v>0.721789879973309</v>
       </c>
       <c r="K47" s="2" t="n">
         <v>0</v>
@@ -2955,31 +2955,31 @@
         <v>-1</v>
       </c>
       <c r="N47" s="2" t="n">
-        <v>-0.008398253518388899</v>
+        <v>0.189438935255743</v>
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="n">
-        <v>6163</v>
+        <v>6259</v>
       </c>
       <c r="B48" s="2" t="inlineStr">
         <is>
-          <t>華電網</t>
+          <t>百徽</t>
         </is>
       </c>
       <c r="C48" s="2" t="n">
         <v/>
       </c>
       <c r="D48" s="2" t="n">
-        <v>362.1327217276552</v>
+        <v>363.2715573028466</v>
       </c>
       <c r="E48" s="2" t="n">
-        <v>41.75</v>
+        <v>29.6</v>
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
@@ -2990,13 +2990,13 @@
         <v>0</v>
       </c>
       <c r="H48" s="2" t="n">
-        <v>46.99368735995021</v>
+        <v>43.22341216105632</v>
       </c>
       <c r="I48" s="2" t="n">
-        <v>18.25977700350222</v>
+        <v>11.52027153639223</v>
       </c>
       <c r="J48" s="2" t="n">
-        <v>0.2067596149695687</v>
+        <v>0.6291044405478855</v>
       </c>
       <c r="K48" s="2" t="n">
         <v>0</v>
@@ -3008,31 +3008,31 @@
         <v>-1</v>
       </c>
       <c r="N48" s="2" t="n">
-        <v>0.3009490946801975</v>
+        <v>-0.008398253518388899</v>
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="n">
-        <v>6182</v>
+        <v>6163</v>
       </c>
       <c r="B49" s="2" t="inlineStr">
         <is>
-          <t>合晶</t>
+          <t>華電網</t>
         </is>
       </c>
       <c r="C49" s="2" t="n">
         <v/>
       </c>
       <c r="D49" s="2" t="n">
-        <v>360.7813027710205</v>
+        <v>362.1327217276552</v>
       </c>
       <c r="E49" s="2" t="n">
-        <v>110</v>
+        <v>41.75</v>
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
@@ -3043,13 +3043,13 @@
         <v>0</v>
       </c>
       <c r="H49" s="2" t="n">
-        <v>48.76522010095545</v>
+        <v>46.99368735995021</v>
       </c>
       <c r="I49" s="2" t="n">
-        <v>15.78560877783874</v>
+        <v>18.25977700350222</v>
       </c>
       <c r="J49" s="2" t="n">
-        <v>2.204799877214242</v>
+        <v>0.2067596149695687</v>
       </c>
       <c r="K49" s="2" t="n">
         <v>0</v>
@@ -3061,31 +3061,31 @@
         <v>-1</v>
       </c>
       <c r="N49" s="2" t="n">
-        <v>1.411325561183938</v>
+        <v>0.3009490946801975</v>
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, volume_break, market_above_ma60, avoid_chase, liquidity_ok, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="n">
-        <v>6263</v>
+        <v>6182</v>
       </c>
       <c r="B50" s="2" t="inlineStr">
         <is>
-          <t>普萊德</t>
+          <t>合晶</t>
         </is>
       </c>
       <c r="C50" s="2" t="n">
         <v/>
       </c>
       <c r="D50" s="2" t="n">
-        <v>360.4313449307242</v>
+        <v>360.7813027710205</v>
       </c>
       <c r="E50" s="2" t="n">
-        <v>161.5</v>
+        <v>110</v>
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
@@ -3096,13 +3096,13 @@
         <v>0</v>
       </c>
       <c r="H50" s="2" t="n">
-        <v>54.14293530509993</v>
+        <v>48.76522010095545</v>
       </c>
       <c r="I50" s="2" t="n">
-        <v>10.43958657358851</v>
+        <v>15.78560877783874</v>
       </c>
       <c r="J50" s="2" t="n">
-        <v>0.483256493262279</v>
+        <v>2.204799877214242</v>
       </c>
       <c r="K50" s="2" t="n">
         <v>0</v>
@@ -3114,31 +3114,31 @@
         <v>-1</v>
       </c>
       <c r="N50" s="2" t="n">
-        <v>0.7899242708275891</v>
+        <v>1.411325561183938</v>
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, volume_break, market_above_ma60, avoid_chase, liquidity_ok, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="n">
-        <v>6432</v>
+        <v>6263</v>
       </c>
       <c r="B51" s="2" t="inlineStr">
         <is>
-          <t>今展科</t>
+          <t>普萊德</t>
         </is>
       </c>
       <c r="C51" s="2" t="n">
         <v/>
       </c>
       <c r="D51" s="2" t="n">
-        <v>359.4827033921836</v>
+        <v>360.4313449307242</v>
       </c>
       <c r="E51" s="2" t="n">
-        <v>64.8</v>
+        <v>161.5</v>
       </c>
       <c r="F51" s="2" t="inlineStr">
         <is>
@@ -3149,13 +3149,13 @@
         <v>0</v>
       </c>
       <c r="H51" s="2" t="n">
-        <v>39.90402785759234</v>
+        <v>54.14293530509993</v>
       </c>
       <c r="I51" s="2" t="n">
-        <v>11.08683797635912</v>
+        <v>10.43958657358851</v>
       </c>
       <c r="J51" s="2" t="n">
-        <v>0.4216393966471793</v>
+        <v>0.483256493262279</v>
       </c>
       <c r="K51" s="2" t="n">
         <v>0</v>
@@ -3167,31 +3167,31 @@
         <v>-1</v>
       </c>
       <c r="N51" s="2" t="n">
-        <v>-0.9233400117084856</v>
+        <v>0.7899242708275891</v>
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="n">
-        <v>6414</v>
+        <v>6432</v>
       </c>
       <c r="B52" s="2" t="inlineStr">
         <is>
-          <t>樺漢</t>
+          <t>今展科</t>
         </is>
       </c>
       <c r="C52" s="2" t="n">
         <v/>
       </c>
       <c r="D52" s="2" t="n">
-        <v>357.2156254917267</v>
+        <v>359.4827033921836</v>
       </c>
       <c r="E52" s="2" t="n">
-        <v>395.5</v>
+        <v>64.8</v>
       </c>
       <c r="F52" s="2" t="inlineStr">
         <is>
@@ -3202,13 +3202,13 @@
         <v>0</v>
       </c>
       <c r="H52" s="2" t="n">
-        <v>42.82885049354655</v>
+        <v>39.90402785759234</v>
       </c>
       <c r="I52" s="2" t="n">
-        <v>18.63537340005778</v>
+        <v>11.08683797635912</v>
       </c>
       <c r="J52" s="2" t="n">
-        <v>0.250269828356257</v>
+        <v>0.4216393966471793</v>
       </c>
       <c r="K52" s="2" t="n">
         <v>0</v>
@@ -3220,31 +3220,31 @@
         <v>-1</v>
       </c>
       <c r="N52" s="2" t="n">
-        <v>-8.539669430806267</v>
+        <v>-0.9233400117084856</v>
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="n">
-        <v>6456</v>
+        <v>6414</v>
       </c>
       <c r="B53" s="2" t="inlineStr">
         <is>
-          <t>GIS-KY</t>
+          <t>樺漢</t>
         </is>
       </c>
       <c r="C53" s="2" t="n">
         <v/>
       </c>
       <c r="D53" s="2" t="n">
-        <v>354.2655703264598</v>
+        <v>357.2156254917267</v>
       </c>
       <c r="E53" s="2" t="n">
-        <v>65.5</v>
+        <v>395.5</v>
       </c>
       <c r="F53" s="2" t="inlineStr">
         <is>
@@ -3255,13 +3255,13 @@
         <v>0</v>
       </c>
       <c r="H53" s="2" t="n">
-        <v>49.99482117368367</v>
+        <v>42.82885049354655</v>
       </c>
       <c r="I53" s="2" t="n">
-        <v>15.40164121734415</v>
+        <v>18.63537340005778</v>
       </c>
       <c r="J53" s="2" t="n">
-        <v>0.8098760833225783</v>
+        <v>0.250269828356257</v>
       </c>
       <c r="K53" s="2" t="n">
         <v>0</v>
@@ -3273,31 +3273,31 @@
         <v>-1</v>
       </c>
       <c r="N53" s="2" t="n">
-        <v>0.6836388564586743</v>
+        <v>-8.539669430806267</v>
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="2" t="n">
-        <v>6470</v>
+        <v>6456</v>
       </c>
       <c r="B54" s="2" t="inlineStr">
         <is>
-          <t>宇智</t>
+          <t>GIS-KY</t>
         </is>
       </c>
       <c r="C54" s="2" t="n">
         <v/>
       </c>
       <c r="D54" s="2" t="n">
-        <v>353.7537822910452</v>
+        <v>354.2655703264598</v>
       </c>
       <c r="E54" s="2" t="n">
-        <v>41.75</v>
+        <v>65.5</v>
       </c>
       <c r="F54" s="2" t="inlineStr">
         <is>
@@ -3308,16 +3308,16 @@
         <v>0</v>
       </c>
       <c r="H54" s="2" t="n">
-        <v>30.64503758453145</v>
+        <v>49.99482117368367</v>
       </c>
       <c r="I54" s="2" t="n">
-        <v>45.25522199648584</v>
+        <v>15.40164121734415</v>
       </c>
       <c r="J54" s="2" t="n">
-        <v>0.1976936783852191</v>
+        <v>0.8098760833225783</v>
       </c>
       <c r="K54" s="2" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="L54" s="2" t="n">
         <v>0</v>
@@ -3326,31 +3326,31 @@
         <v>-1</v>
       </c>
       <c r="N54" s="2" t="n">
-        <v>0.1031701012698258</v>
+        <v>0.6836388564586743</v>
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, foreign_buy_3d, adx_trending, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="n">
-        <v>6243</v>
+        <v>6470</v>
       </c>
       <c r="B55" s="2" t="inlineStr">
         <is>
-          <t>迅杰</t>
+          <t>宇智</t>
         </is>
       </c>
       <c r="C55" s="2" t="n">
         <v/>
       </c>
       <c r="D55" s="2" t="n">
-        <v>349.2978500478916</v>
+        <v>353.7537822910452</v>
       </c>
       <c r="E55" s="2" t="n">
-        <v>41.9</v>
+        <v>41.75</v>
       </c>
       <c r="F55" s="2" t="inlineStr">
         <is>
@@ -3361,16 +3361,16 @@
         <v>0</v>
       </c>
       <c r="H55" s="2" t="n">
-        <v>43.87108578393243</v>
+        <v>30.64503758453145</v>
       </c>
       <c r="I55" s="2" t="n">
-        <v>20.44390561598116</v>
+        <v>45.25522199648584</v>
       </c>
       <c r="J55" s="2" t="n">
-        <v>0.1996377810239122</v>
+        <v>0.1976936783852191</v>
       </c>
       <c r="K55" s="2" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="L55" s="2" t="n">
         <v>0</v>
@@ -3379,31 +3379,31 @@
         <v>-1</v>
       </c>
       <c r="N55" s="2" t="n">
-        <v>-0.8588523289466768</v>
+        <v>0.1031701012698258</v>
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, foreign_buy_3d, adx_trending, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="n">
-        <v>6417</v>
+        <v>6243</v>
       </c>
       <c r="B56" s="2" t="inlineStr">
         <is>
-          <t>韋僑</t>
+          <t>迅杰</t>
         </is>
       </c>
       <c r="C56" s="2" t="n">
         <v/>
       </c>
       <c r="D56" s="2" t="n">
-        <v>346.4092271611214</v>
+        <v>349.2978500478916</v>
       </c>
       <c r="E56" s="2" t="n">
-        <v>109</v>
+        <v>41.9</v>
       </c>
       <c r="F56" s="2" t="inlineStr">
         <is>
@@ -3414,13 +3414,13 @@
         <v>0</v>
       </c>
       <c r="H56" s="2" t="n">
-        <v>40.53951846357658</v>
+        <v>43.87108578393243</v>
       </c>
       <c r="I56" s="2" t="n">
-        <v>22.98366773628046</v>
+        <v>20.44390561598116</v>
       </c>
       <c r="J56" s="2" t="n">
-        <v>0.2342271662502479</v>
+        <v>0.1996377810239122</v>
       </c>
       <c r="K56" s="2" t="n">
         <v>0</v>
@@ -3432,31 +3432,31 @@
         <v>-1</v>
       </c>
       <c r="N56" s="2" t="n">
-        <v>0.2636795483665279</v>
+        <v>-0.8588523289466768</v>
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="n">
-        <v>6209</v>
+        <v>6417</v>
       </c>
       <c r="B57" s="2" t="inlineStr">
         <is>
-          <t>今國光</t>
+          <t>韋僑</t>
         </is>
       </c>
       <c r="C57" s="2" t="n">
         <v/>
       </c>
       <c r="D57" s="2" t="n">
-        <v>345.659656738294</v>
+        <v>346.4092271611214</v>
       </c>
       <c r="E57" s="2" t="n">
-        <v>67.8</v>
+        <v>109</v>
       </c>
       <c r="F57" s="2" t="inlineStr">
         <is>
@@ -3467,13 +3467,13 @@
         <v>0</v>
       </c>
       <c r="H57" s="2" t="n">
-        <v>44.36687961592656</v>
+        <v>40.53951846357658</v>
       </c>
       <c r="I57" s="2" t="n">
-        <v>12.5224780031729</v>
+        <v>22.98366773628046</v>
       </c>
       <c r="J57" s="2" t="n">
-        <v>0.657107791777923</v>
+        <v>0.2342271662502479</v>
       </c>
       <c r="K57" s="2" t="n">
         <v>0</v>
@@ -3485,31 +3485,31 @@
         <v>-1</v>
       </c>
       <c r="N57" s="2" t="n">
-        <v>0.009269115682231901</v>
+        <v>0.2636795483665279</v>
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="n">
-        <v>6215</v>
+        <v>6209</v>
       </c>
       <c r="B58" s="2" t="inlineStr">
         <is>
-          <t>和椿</t>
+          <t>今國光</t>
         </is>
       </c>
       <c r="C58" s="2" t="n">
         <v/>
       </c>
       <c r="D58" s="2" t="n">
-        <v>345.2861989895901</v>
+        <v>345.659656738294</v>
       </c>
       <c r="E58" s="2" t="n">
-        <v>96.09999999999999</v>
+        <v>67.8</v>
       </c>
       <c r="F58" s="2" t="inlineStr">
         <is>
@@ -3520,13 +3520,13 @@
         <v>0</v>
       </c>
       <c r="H58" s="2" t="n">
-        <v>43.61091324047195</v>
+        <v>44.36687961592656</v>
       </c>
       <c r="I58" s="2" t="n">
-        <v>15.78654676509929</v>
+        <v>12.5224780031729</v>
       </c>
       <c r="J58" s="2" t="n">
-        <v>0.3114857910635454</v>
+        <v>0.657107791777923</v>
       </c>
       <c r="K58" s="2" t="n">
         <v>0</v>
@@ -3538,31 +3538,31 @@
         <v>-1</v>
       </c>
       <c r="N58" s="2" t="n">
-        <v>0.1560120894572898</v>
+        <v>0.009269115682231901</v>
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="2" t="n">
-        <v>6281</v>
+        <v>6215</v>
       </c>
       <c r="B59" s="2" t="inlineStr">
         <is>
-          <t>全國電</t>
+          <t>和椿</t>
         </is>
       </c>
       <c r="C59" s="2" t="n">
         <v/>
       </c>
       <c r="D59" s="2" t="n">
-        <v>344.8130275801932</v>
+        <v>345.2861989895901</v>
       </c>
       <c r="E59" s="2" t="n">
-        <v>51.8</v>
+        <v>96.09999999999999</v>
       </c>
       <c r="F59" s="2" t="inlineStr">
         <is>
@@ -3573,13 +3573,13 @@
         <v>0</v>
       </c>
       <c r="H59" s="2" t="n">
-        <v>54.05055726857766</v>
+        <v>43.61091324047195</v>
       </c>
       <c r="I59" s="2" t="n">
-        <v>15.82180482580008</v>
+        <v>15.78654676509929</v>
       </c>
       <c r="J59" s="2" t="n">
-        <v>0.6898989278093415</v>
+        <v>0.3114857910635454</v>
       </c>
       <c r="K59" s="2" t="n">
         <v>0</v>
@@ -3591,31 +3591,31 @@
         <v>-1</v>
       </c>
       <c r="N59" s="2" t="n">
-        <v>0.011020688120182</v>
+        <v>0.1560120894572898</v>
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>macd_golden_cross, market_above_ma60, avoid_chase, hist_turn_positive, above_ichimoku_cloud</t>
+          <t>market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="2" t="n">
-        <v>6198</v>
+        <v>6281</v>
       </c>
       <c r="B60" s="2" t="inlineStr">
         <is>
-          <t>瑞築</t>
+          <t>全國電</t>
         </is>
       </c>
       <c r="C60" s="2" t="n">
         <v/>
       </c>
       <c r="D60" s="2" t="n">
-        <v>343.8996097932338</v>
+        <v>344.8130275801932</v>
       </c>
       <c r="E60" s="2" t="n">
-        <v>19.5</v>
+        <v>51.8</v>
       </c>
       <c r="F60" s="2" t="inlineStr">
         <is>
@@ -3626,13 +3626,13 @@
         <v>0</v>
       </c>
       <c r="H60" s="2" t="n">
-        <v>51.56285805371847</v>
+        <v>54.05055726857766</v>
       </c>
       <c r="I60" s="2" t="n">
-        <v>6.320693654162163</v>
+        <v>15.82180482580008</v>
       </c>
       <c r="J60" s="2" t="n">
-        <v>1.501873658693887</v>
+        <v>0.6898989278093415</v>
       </c>
       <c r="K60" s="2" t="n">
         <v>0</v>
@@ -3644,31 +3644,31 @@
         <v>-1</v>
       </c>
       <c r="N60" s="2" t="n">
-        <v>0.4416182542964587</v>
+        <v>0.011020688120182</v>
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>volume_break, market_above_ma60, avoid_chase, obv_uptrend, above_ichimoku_cloud</t>
+          <t>macd_golden_cross, market_above_ma60, avoid_chase, hist_turn_positive, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="2" t="n">
-        <v>6230</v>
+        <v>6198</v>
       </c>
       <c r="B61" s="2" t="inlineStr">
         <is>
-          <t>尼得科超眾</t>
+          <t>瑞築</t>
         </is>
       </c>
       <c r="C61" s="2" t="n">
         <v/>
       </c>
       <c r="D61" s="2" t="n">
-        <v>343.3410407780669</v>
+        <v>343.8996097932338</v>
       </c>
       <c r="E61" s="2" t="n">
-        <v>107</v>
+        <v>19.5</v>
       </c>
       <c r="F61" s="2" t="inlineStr">
         <is>
@@ -3679,13 +3679,13 @@
         <v>0</v>
       </c>
       <c r="H61" s="2" t="n">
-        <v>41.30572830886945</v>
+        <v>51.56285805371847</v>
       </c>
       <c r="I61" s="2" t="n">
-        <v>20.20883793851421</v>
+        <v>6.320693654162163</v>
       </c>
       <c r="J61" s="2" t="n">
-        <v>0.1416302546331173</v>
+        <v>1.501873658693887</v>
       </c>
       <c r="K61" s="2" t="n">
         <v>0</v>
@@ -3697,31 +3697,31 @@
         <v>-1</v>
       </c>
       <c r="N61" s="2" t="n">
-        <v>0.3708529853923092</v>
+        <v>0.4416182542964587</v>
       </c>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>volume_break, market_above_ma60, avoid_chase, obv_uptrend, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="2" t="n">
-        <v>6202</v>
+        <v>6230</v>
       </c>
       <c r="B62" s="2" t="inlineStr">
         <is>
-          <t>盛群</t>
+          <t>尼得科超眾</t>
         </is>
       </c>
       <c r="C62" s="2" t="n">
         <v/>
       </c>
       <c r="D62" s="2" t="n">
-        <v>341.5933121166568</v>
+        <v>343.3410407780669</v>
       </c>
       <c r="E62" s="2" t="n">
-        <v>56.2</v>
+        <v>107</v>
       </c>
       <c r="F62" s="2" t="inlineStr">
         <is>
@@ -3732,13 +3732,13 @@
         <v>0</v>
       </c>
       <c r="H62" s="2" t="n">
-        <v>44.04582881808587</v>
+        <v>41.30572830886945</v>
       </c>
       <c r="I62" s="2" t="n">
-        <v>15.2604476716629</v>
+        <v>20.20883793851421</v>
       </c>
       <c r="J62" s="2" t="n">
-        <v>0.2340044428925392</v>
+        <v>0.1416302546331173</v>
       </c>
       <c r="K62" s="2" t="n">
         <v>0</v>
@@ -3750,31 +3750,31 @@
         <v>-1</v>
       </c>
       <c r="N62" s="2" t="n">
-        <v>-0.2581135108015367</v>
+        <v>0.3708529853923092</v>
       </c>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="2" t="n">
-        <v>6284</v>
+        <v>6202</v>
       </c>
       <c r="B63" s="2" t="inlineStr">
         <is>
-          <t>佳邦</t>
+          <t>盛群</t>
         </is>
       </c>
       <c r="C63" s="2" t="n">
         <v/>
       </c>
       <c r="D63" s="2" t="n">
-        <v>341.4417790222048</v>
+        <v>341.5933121166568</v>
       </c>
       <c r="E63" s="2" t="n">
-        <v>74.8</v>
+        <v>56.2</v>
       </c>
       <c r="F63" s="2" t="inlineStr">
         <is>
@@ -3785,13 +3785,13 @@
         <v>0</v>
       </c>
       <c r="H63" s="2" t="n">
-        <v>42.35037714153782</v>
+        <v>44.04582881808587</v>
       </c>
       <c r="I63" s="2" t="n">
-        <v>19.58334410361669</v>
+        <v>15.2604476716629</v>
       </c>
       <c r="J63" s="2" t="n">
-        <v>0.506948635649723</v>
+        <v>0.2340044428925392</v>
       </c>
       <c r="K63" s="2" t="n">
         <v>0</v>
@@ -3803,31 +3803,31 @@
         <v>-1</v>
       </c>
       <c r="N63" s="2" t="n">
-        <v>0.6925899086920353</v>
+        <v>-0.2581135108015367</v>
       </c>
       <c r="O63" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="2" t="n">
-        <v>6477</v>
+        <v>6284</v>
       </c>
       <c r="B64" s="2" t="inlineStr">
         <is>
-          <t>安集</t>
+          <t>佳邦</t>
         </is>
       </c>
       <c r="C64" s="2" t="n">
         <v/>
       </c>
       <c r="D64" s="2" t="n">
-        <v>341.1850388402045</v>
+        <v>341.4417790222048</v>
       </c>
       <c r="E64" s="2" t="n">
-        <v>35.95</v>
+        <v>74.8</v>
       </c>
       <c r="F64" s="2" t="inlineStr">
         <is>
@@ -3838,13 +3838,13 @@
         <v>0</v>
       </c>
       <c r="H64" s="2" t="n">
-        <v>48.0078711916281</v>
+        <v>42.35037714153782</v>
       </c>
       <c r="I64" s="2" t="n">
-        <v>18.52928905904891</v>
+        <v>19.58334410361669</v>
       </c>
       <c r="J64" s="2" t="n">
-        <v>0.3526446630917442</v>
+        <v>0.506948635649723</v>
       </c>
       <c r="K64" s="2" t="n">
         <v>0</v>
@@ -3856,31 +3856,31 @@
         <v>-1</v>
       </c>
       <c r="N64" s="2" t="n">
-        <v>0.1152727040434029</v>
+        <v>0.6925899086920353</v>
       </c>
       <c r="O64" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="2" t="n">
-        <v>6177</v>
+        <v>6477</v>
       </c>
       <c r="B65" s="2" t="inlineStr">
         <is>
-          <t>達麗</t>
+          <t>安集</t>
         </is>
       </c>
       <c r="C65" s="2" t="n">
         <v/>
       </c>
       <c r="D65" s="2" t="n">
-        <v>340.0157493505301</v>
+        <v>341.1850388402045</v>
       </c>
       <c r="E65" s="2" t="n">
-        <v>47.2</v>
+        <v>35.95</v>
       </c>
       <c r="F65" s="2" t="inlineStr">
         <is>
@@ -3891,13 +3891,13 @@
         <v>0</v>
       </c>
       <c r="H65" s="2" t="n">
-        <v>47.05000068115906</v>
+        <v>48.0078711916281</v>
       </c>
       <c r="I65" s="2" t="n">
-        <v>23.40265592858719</v>
+        <v>18.52928905904891</v>
       </c>
       <c r="J65" s="2" t="n">
-        <v>0.6789675392457355</v>
+        <v>0.3526446630917442</v>
       </c>
       <c r="K65" s="2" t="n">
         <v>0</v>
@@ -3909,51 +3909,51 @@
         <v>-1</v>
       </c>
       <c r="N65" s="2" t="n">
-        <v>-0.1497644786860633</v>
+        <v>0.1152727040434029</v>
       </c>
       <c r="O65" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="2" t="n">
-        <v>6241</v>
+        <v>6177</v>
       </c>
       <c r="B66" s="2" t="inlineStr">
         <is>
-          <t>鑫永洋</t>
+          <t>達麗</t>
         </is>
       </c>
       <c r="C66" s="2" t="n">
         <v/>
       </c>
       <c r="D66" s="2" t="n">
-        <v>325.5169087677943</v>
+        <v>340.0157493505301</v>
       </c>
       <c r="E66" s="2" t="n">
-        <v>13.85</v>
+        <v>47.2</v>
       </c>
       <c r="F66" s="2" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="G66" s="2" t="b">
         <v>0</v>
       </c>
       <c r="H66" s="2" t="n">
-        <v>37.93434003937257</v>
+        <v>47.05000068115906</v>
       </c>
       <c r="I66" s="2" t="n">
-        <v>23.71245675465922</v>
+        <v>23.40265592858719</v>
       </c>
       <c r="J66" s="2" t="n">
-        <v>0.9224191436906496</v>
+        <v>0.6789675392457355</v>
       </c>
       <c r="K66" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L66" s="2" t="n">
         <v>0</v>
@@ -3962,51 +3962,51 @@
         <v>-1</v>
       </c>
       <c r="N66" s="2" t="n">
-        <v>-0.3588733292489128</v>
+        <v>-0.1497644786860633</v>
       </c>
       <c r="O66" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="2" t="n">
-        <v>6239</v>
+        <v>6241</v>
       </c>
       <c r="B67" s="2" t="inlineStr">
         <is>
-          <t>力成</t>
+          <t>鑫永洋</t>
         </is>
       </c>
       <c r="C67" s="2" t="n">
         <v/>
       </c>
       <c r="D67" s="2" t="n">
-        <v>321.1770225185937</v>
+        <v>325.5169087677943</v>
       </c>
       <c r="E67" s="2" t="n">
-        <v>269.5</v>
+        <v>13.85</v>
       </c>
       <c r="F67" s="2" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="G67" s="2" t="b">
         <v>0</v>
       </c>
       <c r="H67" s="2" t="n">
-        <v>47.2317410114029</v>
+        <v>37.93434003937257</v>
       </c>
       <c r="I67" s="2" t="n">
-        <v>14.45302043490498</v>
+        <v>23.71245675465922</v>
       </c>
       <c r="J67" s="2" t="n">
-        <v>0.4795678901105257</v>
+        <v>0.9224191436906496</v>
       </c>
       <c r="K67" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L67" s="2" t="n">
         <v>0</v>
@@ -4015,31 +4015,31 @@
         <v>-1</v>
       </c>
       <c r="N67" s="2" t="n">
-        <v>1.814169567916728</v>
+        <v>-0.3588733292489128</v>
       </c>
       <c r="O67" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="2" t="n">
-        <v>6441</v>
+        <v>6239</v>
       </c>
       <c r="B68" s="2" t="inlineStr">
         <is>
-          <t>廣錠</t>
+          <t>力成</t>
         </is>
       </c>
       <c r="C68" s="2" t="n">
         <v/>
       </c>
       <c r="D68" s="2" t="n">
-        <v>318.9323700561681</v>
+        <v>321.1770225185937</v>
       </c>
       <c r="E68" s="2" t="n">
-        <v>21.6</v>
+        <v>269.5</v>
       </c>
       <c r="F68" s="2" t="inlineStr">
         <is>
@@ -4050,13 +4050,13 @@
         <v>0</v>
       </c>
       <c r="H68" s="2" t="n">
-        <v>49.43503910274001</v>
+        <v>47.2317410114029</v>
       </c>
       <c r="I68" s="2" t="n">
-        <v>22.29251407387759</v>
+        <v>14.45302043490498</v>
       </c>
       <c r="J68" s="2" t="n">
-        <v>0.0785284721550091</v>
+        <v>0.4795678901105257</v>
       </c>
       <c r="K68" s="2" t="n">
         <v>0</v>
@@ -4068,31 +4068,31 @@
         <v>-1</v>
       </c>
       <c r="N68" s="2" t="n">
-        <v>0.0360587060875477</v>
+        <v>1.814169567916728</v>
       </c>
       <c r="O68" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="2" t="n">
-        <v>6191</v>
+        <v>6441</v>
       </c>
       <c r="B69" s="2" t="inlineStr">
         <is>
-          <t>精成科</t>
+          <t>廣錠</t>
         </is>
       </c>
       <c r="C69" s="2" t="n">
         <v/>
       </c>
       <c r="D69" s="2" t="n">
-        <v>313.7151820149905</v>
+        <v>318.9323700561681</v>
       </c>
       <c r="E69" s="2" t="n">
-        <v>81.09999999999999</v>
+        <v>21.6</v>
       </c>
       <c r="F69" s="2" t="inlineStr">
         <is>
@@ -4103,13 +4103,13 @@
         <v>0</v>
       </c>
       <c r="H69" s="2" t="n">
-        <v>35.40119024693738</v>
+        <v>49.43503910274001</v>
       </c>
       <c r="I69" s="2" t="n">
-        <v>27.95154092481872</v>
+        <v>22.29251407387759</v>
       </c>
       <c r="J69" s="2" t="n">
-        <v>0.4199261333743641</v>
+        <v>0.0785284721550091</v>
       </c>
       <c r="K69" s="2" t="n">
         <v>0</v>
@@ -4121,31 +4121,31 @@
         <v>-1</v>
       </c>
       <c r="N69" s="2" t="n">
-        <v>0.1401053213482126</v>
+        <v>0.0360587060875477</v>
       </c>
       <c r="O69" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok, adx_trending</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="2" t="n">
-        <v>6411</v>
+        <v>6191</v>
       </c>
       <c r="B70" s="2" t="inlineStr">
         <is>
-          <t>晶焱</t>
+          <t>精成科</t>
         </is>
       </c>
       <c r="C70" s="2" t="n">
         <v/>
       </c>
       <c r="D70" s="2" t="n">
-        <v>312.2048214427978</v>
+        <v>313.7151820149905</v>
       </c>
       <c r="E70" s="2" t="n">
-        <v>77.5</v>
+        <v>81.09999999999999</v>
       </c>
       <c r="F70" s="2" t="inlineStr">
         <is>
@@ -4156,13 +4156,13 @@
         <v>0</v>
       </c>
       <c r="H70" s="2" t="n">
-        <v>42.93680700188347</v>
+        <v>35.40119024693738</v>
       </c>
       <c r="I70" s="2" t="n">
-        <v>18.19444440210598</v>
+        <v>27.95154092481872</v>
       </c>
       <c r="J70" s="2" t="n">
-        <v>0.4838435013465052</v>
+        <v>0.4199261333743641</v>
       </c>
       <c r="K70" s="2" t="n">
         <v>0</v>
@@ -4174,31 +4174,31 @@
         <v>-1</v>
       </c>
       <c r="N70" s="2" t="n">
-        <v>0.7449578477330503</v>
+        <v>0.1401053213482126</v>
       </c>
       <c r="O70" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, liquidity_ok, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="2" t="n">
-        <v>6204</v>
+        <v>6411</v>
       </c>
       <c r="B71" s="2" t="inlineStr">
         <is>
-          <t>艾華</t>
+          <t>晶焱</t>
         </is>
       </c>
       <c r="C71" s="2" t="n">
         <v/>
       </c>
       <c r="D71" s="2" t="n">
-        <v>310.7964553227353</v>
+        <v>312.2048214427978</v>
       </c>
       <c r="E71" s="2" t="n">
-        <v>84.90000000000001</v>
+        <v>77.5</v>
       </c>
       <c r="F71" s="2" t="inlineStr">
         <is>
@@ -4209,13 +4209,13 @@
         <v>0</v>
       </c>
       <c r="H71" s="2" t="n">
-        <v>53.26617735647122</v>
+        <v>42.93680700188347</v>
       </c>
       <c r="I71" s="2" t="n">
-        <v>19.53607675721564</v>
+        <v>18.19444440210598</v>
       </c>
       <c r="J71" s="2" t="n">
-        <v>1.054595776405039</v>
+        <v>0.4838435013465052</v>
       </c>
       <c r="K71" s="2" t="n">
         <v>0</v>
@@ -4227,31 +4227,31 @@
         <v>-1</v>
       </c>
       <c r="N71" s="2" t="n">
-        <v>1.869963660319002</v>
+        <v>0.7449578477330503</v>
       </c>
       <c r="O71" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, obv_uptrend, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="2" t="n">
-        <v>6418</v>
+        <v>6204</v>
       </c>
       <c r="B72" s="2" t="inlineStr">
         <is>
-          <t>詠昇</t>
+          <t>艾華</t>
         </is>
       </c>
       <c r="C72" s="2" t="n">
         <v/>
       </c>
       <c r="D72" s="2" t="n">
-        <v>305.4545223458632</v>
+        <v>310.7964553227353</v>
       </c>
       <c r="E72" s="2" t="n">
-        <v>32.3</v>
+        <v>84.90000000000001</v>
       </c>
       <c r="F72" s="2" t="inlineStr">
         <is>
@@ -4262,13 +4262,13 @@
         <v>0</v>
       </c>
       <c r="H72" s="2" t="n">
-        <v>52.43075988077417</v>
+        <v>53.26617735647122</v>
       </c>
       <c r="I72" s="2" t="n">
-        <v>19.85079442508682</v>
+        <v>19.53607675721564</v>
       </c>
       <c r="J72" s="2" t="n">
-        <v>0.7150646411302768</v>
+        <v>1.054595776405039</v>
       </c>
       <c r="K72" s="2" t="n">
         <v>0</v>
@@ -4280,31 +4280,31 @@
         <v>-1</v>
       </c>
       <c r="N72" s="2" t="n">
-        <v>0.125418561929403</v>
+        <v>1.869963660319002</v>
       </c>
       <c r="O72" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="2" t="n">
-        <v>6266</v>
+        <v>6418</v>
       </c>
       <c r="B73" s="2" t="inlineStr">
         <is>
-          <t>泰詠</t>
+          <t>詠昇</t>
         </is>
       </c>
       <c r="C73" s="2" t="n">
         <v/>
       </c>
       <c r="D73" s="2" t="n">
-        <v>294.533574875642</v>
+        <v>305.4545223458632</v>
       </c>
       <c r="E73" s="2" t="n">
-        <v>25.15</v>
+        <v>32.3</v>
       </c>
       <c r="F73" s="2" t="inlineStr">
         <is>
@@ -4315,13 +4315,13 @@
         <v>0</v>
       </c>
       <c r="H73" s="2" t="n">
-        <v>53.1691694976995</v>
+        <v>52.43075988077417</v>
       </c>
       <c r="I73" s="2" t="n">
-        <v>12.40089586621029</v>
+        <v>19.85079442508682</v>
       </c>
       <c r="J73" s="2" t="n">
-        <v>0.4884710338530217</v>
+        <v>0.7150646411302768</v>
       </c>
       <c r="K73" s="2" t="n">
         <v>0</v>
@@ -4333,7 +4333,7 @@
         <v>-1</v>
       </c>
       <c r="N73" s="2" t="n">
-        <v>0.1005220832560411</v>
+        <v>0.125418561929403</v>
       </c>
       <c r="O73" s="2" t="inlineStr">
         <is>
@@ -4343,21 +4343,21 @@
     </row>
     <row r="74">
       <c r="A74" s="2" t="n">
-        <v>6192</v>
+        <v>6266</v>
       </c>
       <c r="B74" s="2" t="inlineStr">
         <is>
-          <t>巨路</t>
+          <t>泰詠</t>
         </is>
       </c>
       <c r="C74" s="2" t="n">
         <v/>
       </c>
       <c r="D74" s="2" t="n">
-        <v>291.4799006912023</v>
+        <v>294.533574875642</v>
       </c>
       <c r="E74" s="2" t="n">
-        <v>116</v>
+        <v>25.15</v>
       </c>
       <c r="F74" s="2" t="inlineStr">
         <is>
@@ -4368,13 +4368,13 @@
         <v>0</v>
       </c>
       <c r="H74" s="2" t="n">
-        <v>48.72449163360349</v>
+        <v>53.1691694976995</v>
       </c>
       <c r="I74" s="2" t="n">
-        <v>19.10134483444362</v>
+        <v>12.40089586621029</v>
       </c>
       <c r="J74" s="2" t="n">
-        <v>0.2828628403676352</v>
+        <v>0.4884710338530217</v>
       </c>
       <c r="K74" s="2" t="n">
         <v>0</v>
@@ -4386,7 +4386,7 @@
         <v>-1</v>
       </c>
       <c r="N74" s="2" t="n">
-        <v>0.2354413304658614</v>
+        <v>0.1005220832560411</v>
       </c>
       <c r="O74" s="2" t="inlineStr">
         <is>
@@ -4396,21 +4396,21 @@
     </row>
     <row r="75">
       <c r="A75" s="2" t="n">
-        <v>6423</v>
+        <v>6192</v>
       </c>
       <c r="B75" s="2" t="inlineStr">
         <is>
-          <t>億而得-創</t>
+          <t>巨路</t>
         </is>
       </c>
       <c r="C75" s="2" t="n">
         <v/>
       </c>
       <c r="D75" s="2" t="n">
-        <v>288.1274461090862</v>
+        <v>291.4799006912023</v>
       </c>
       <c r="E75" s="2" t="n">
-        <v>79.40000000000001</v>
+        <v>116</v>
       </c>
       <c r="F75" s="2" t="inlineStr">
         <is>
@@ -4421,13 +4421,13 @@
         <v>0</v>
       </c>
       <c r="H75" s="2" t="n">
-        <v>53.93972719337613</v>
+        <v>48.72449163360349</v>
       </c>
       <c r="I75" s="2" t="n">
-        <v>16.6039334013711</v>
+        <v>19.10134483444362</v>
       </c>
       <c r="J75" s="2" t="n">
-        <v>0.6395825730009431</v>
+        <v>0.2828628403676352</v>
       </c>
       <c r="K75" s="2" t="n">
         <v>0</v>
@@ -4439,7 +4439,7 @@
         <v>-1</v>
       </c>
       <c r="N75" s="2" t="n">
-        <v>0.5002515018493005</v>
+        <v>0.2354413304658614</v>
       </c>
       <c r="O75" s="2" t="inlineStr">
         <is>
@@ -4449,21 +4449,21 @@
     </row>
     <row r="76">
       <c r="A76" s="2" t="n">
-        <v>6233</v>
+        <v>6423</v>
       </c>
       <c r="B76" s="2" t="inlineStr">
         <is>
-          <t>旺玖</t>
+          <t>億而得-創</t>
         </is>
       </c>
       <c r="C76" s="2" t="n">
         <v/>
       </c>
       <c r="D76" s="2" t="n">
-        <v>287.2167962063328</v>
+        <v>288.1274461090862</v>
       </c>
       <c r="E76" s="2" t="n">
-        <v>21.25</v>
+        <v>79.40000000000001</v>
       </c>
       <c r="F76" s="2" t="inlineStr">
         <is>
@@ -4474,13 +4474,13 @@
         <v>0</v>
       </c>
       <c r="H76" s="2" t="n">
-        <v>45.53167047865959</v>
+        <v>53.93972719337613</v>
       </c>
       <c r="I76" s="2" t="n">
-        <v>18.89517175603767</v>
+        <v>16.6039334013711</v>
       </c>
       <c r="J76" s="2" t="n">
-        <v>0.782346957793464</v>
+        <v>0.6395825730009431</v>
       </c>
       <c r="K76" s="2" t="n">
         <v>0</v>
@@ -4492,31 +4492,31 @@
         <v>-1</v>
       </c>
       <c r="N76" s="2" t="n">
-        <v>0.1273242818256004</v>
+        <v>0.5002515018493005</v>
       </c>
       <c r="O76" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, kd_golden_cross, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="2" t="n">
-        <v>6270</v>
+        <v>6233</v>
       </c>
       <c r="B77" s="2" t="inlineStr">
         <is>
-          <t>倍微</t>
+          <t>旺玖</t>
         </is>
       </c>
       <c r="C77" s="2" t="n">
         <v/>
       </c>
       <c r="D77" s="2" t="n">
-        <v>283.7797636433349</v>
+        <v>287.2167962063328</v>
       </c>
       <c r="E77" s="2" t="n">
-        <v>29.2</v>
+        <v>21.25</v>
       </c>
       <c r="F77" s="2" t="inlineStr">
         <is>
@@ -4527,13 +4527,13 @@
         <v>0</v>
       </c>
       <c r="H77" s="2" t="n">
-        <v>42.48876915428093</v>
+        <v>45.53167047865959</v>
       </c>
       <c r="I77" s="2" t="n">
-        <v>10.6254020648229</v>
+        <v>18.89517175603767</v>
       </c>
       <c r="J77" s="2" t="n">
-        <v>0.4228440935479814</v>
+        <v>0.782346957793464</v>
       </c>
       <c r="K77" s="2" t="n">
         <v>0</v>
@@ -4545,31 +4545,31 @@
         <v>-1</v>
       </c>
       <c r="N77" s="2" t="n">
-        <v>0.1532052943582431</v>
+        <v>0.1273242818256004</v>
       </c>
       <c r="O77" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, kd_golden_cross, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="2" t="n">
-        <v>6216</v>
+        <v>6270</v>
       </c>
       <c r="B78" s="2" t="inlineStr">
         <is>
-          <t>居易</t>
+          <t>倍微</t>
         </is>
       </c>
       <c r="C78" s="2" t="n">
         <v/>
       </c>
       <c r="D78" s="2" t="n">
-        <v>283.0497646636455</v>
+        <v>283.7797636433349</v>
       </c>
       <c r="E78" s="2" t="n">
-        <v>22.4</v>
+        <v>29.2</v>
       </c>
       <c r="F78" s="2" t="inlineStr">
         <is>
@@ -4580,13 +4580,13 @@
         <v>0</v>
       </c>
       <c r="H78" s="2" t="n">
-        <v>53.31704834215956</v>
+        <v>42.48876915428093</v>
       </c>
       <c r="I78" s="2" t="n">
-        <v>10.66975501510525</v>
+        <v>10.6254020648229</v>
       </c>
       <c r="J78" s="2" t="n">
-        <v>0.4861110588667214</v>
+        <v>0.4228440935479814</v>
       </c>
       <c r="K78" s="2" t="n">
         <v>0</v>
@@ -4598,31 +4598,31 @@
         <v>-1</v>
       </c>
       <c r="N78" s="2" t="n">
-        <v>0.0555990165228242</v>
+        <v>0.1532052943582431</v>
       </c>
       <c r="O78" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="2" t="n">
-        <v>6442</v>
+        <v>6216</v>
       </c>
       <c r="B79" s="2" t="inlineStr">
         <is>
-          <t>光聖</t>
+          <t>居易</t>
         </is>
       </c>
       <c r="C79" s="2" t="n">
         <v/>
       </c>
       <c r="D79" s="2" t="n">
-        <v>278.5034737474433</v>
+        <v>283.0497646636455</v>
       </c>
       <c r="E79" s="2" t="n">
-        <v>1460</v>
+        <v>22.4</v>
       </c>
       <c r="F79" s="2" t="inlineStr">
         <is>
@@ -4633,13 +4633,13 @@
         <v>0</v>
       </c>
       <c r="H79" s="2" t="n">
-        <v>49.13159561179232</v>
+        <v>53.31704834215956</v>
       </c>
       <c r="I79" s="2" t="n">
-        <v>18.77684503716942</v>
+        <v>10.66975501510525</v>
       </c>
       <c r="J79" s="2" t="n">
-        <v>0.4125280924000814</v>
+        <v>0.4861110588667214</v>
       </c>
       <c r="K79" s="2" t="n">
         <v>0</v>
@@ -4651,31 +4651,31 @@
         <v>-1</v>
       </c>
       <c r="N79" s="2" t="n">
-        <v>18.24307738529228</v>
+        <v>0.0555990165228242</v>
       </c>
       <c r="O79" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="2" t="n">
-        <v>6217</v>
+        <v>6442</v>
       </c>
       <c r="B80" s="2" t="inlineStr">
         <is>
-          <t>中探針</t>
+          <t>光聖</t>
         </is>
       </c>
       <c r="C80" s="2" t="n">
         <v/>
       </c>
       <c r="D80" s="2" t="n">
-        <v>276.2141427471759</v>
+        <v>278.5034737474433</v>
       </c>
       <c r="E80" s="2" t="n">
-        <v>148</v>
+        <v>1460</v>
       </c>
       <c r="F80" s="2" t="inlineStr">
         <is>
@@ -4686,13 +4686,13 @@
         <v>0</v>
       </c>
       <c r="H80" s="2" t="n">
-        <v>40.99642576613015</v>
+        <v>49.13159561179232</v>
       </c>
       <c r="I80" s="2" t="n">
-        <v>14.7877304719607</v>
+        <v>18.77684503716942</v>
       </c>
       <c r="J80" s="2" t="n">
-        <v>1.116413385531702</v>
+        <v>0.4125280924000814</v>
       </c>
       <c r="K80" s="2" t="n">
         <v>0</v>
@@ -4704,51 +4704,51 @@
         <v>-1</v>
       </c>
       <c r="N80" s="2" t="n">
-        <v>3.235900239770192</v>
+        <v>18.24307738529228</v>
       </c>
       <c r="O80" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok</t>
+          <t>market_above_ma60, avoid_chase, liquidity_ok, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="2" t="n">
-        <v>6288</v>
+        <v>6217</v>
       </c>
       <c r="B81" s="2" t="inlineStr">
         <is>
-          <t>聯嘉</t>
+          <t>中探針</t>
         </is>
       </c>
       <c r="C81" s="2" t="n">
         <v/>
       </c>
       <c r="D81" s="2" t="n">
-        <v>274.7461384602392</v>
+        <v>276.2141427471759</v>
       </c>
       <c r="E81" s="2" t="n">
-        <v>20.95</v>
+        <v>148</v>
       </c>
       <c r="F81" s="2" t="inlineStr">
         <is>
-          <t>2025-08-04</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="G81" s="2" t="b">
         <v>0</v>
       </c>
       <c r="H81" s="2" t="n">
-        <v>52.36103162055688</v>
+        <v>40.99642576613015</v>
       </c>
       <c r="I81" s="2" t="n">
-        <v/>
+        <v>14.7877304719607</v>
       </c>
       <c r="J81" s="2" t="n">
-        <v>0.6831032524092705</v>
+        <v>1.116413385531702</v>
       </c>
       <c r="K81" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L81" s="2" t="n">
         <v>0</v>
@@ -4757,51 +4757,51 @@
         <v>-1</v>
       </c>
       <c r="N81" s="2" t="n">
-        <v>0.0151614614171343</v>
+        <v>3.235900239770192</v>
       </c>
       <c r="O81" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, avoid_chase, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="2" t="n">
-        <v>6257</v>
+        <v>6288</v>
       </c>
       <c r="B82" s="2" t="inlineStr">
         <is>
-          <t>矽格</t>
+          <t>聯嘉</t>
         </is>
       </c>
       <c r="C82" s="2" t="n">
         <v/>
       </c>
       <c r="D82" s="2" t="n">
-        <v>273.502986139914</v>
+        <v>274.7461384602392</v>
       </c>
       <c r="E82" s="2" t="n">
-        <v>197.5</v>
+        <v>20.95</v>
       </c>
       <c r="F82" s="2" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2025-08-04</t>
         </is>
       </c>
       <c r="G82" s="2" t="b">
         <v>0</v>
       </c>
       <c r="H82" s="2" t="n">
-        <v>42.93069144705502</v>
+        <v>52.36103162055688</v>
       </c>
       <c r="I82" s="2" t="n">
-        <v>14.35913194971289</v>
+        <v/>
       </c>
       <c r="J82" s="2" t="n">
-        <v>0.4136491083731533</v>
+        <v>0.6831032524092705</v>
       </c>
       <c r="K82" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L82" s="2" t="n">
         <v>0</v>
@@ -4810,31 +4810,31 @@
         <v>-1</v>
       </c>
       <c r="N82" s="2" t="n">
-        <v>0.294254828683421</v>
+        <v>0.0151614614171343</v>
       </c>
       <c r="O82" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok</t>
+          <t>ema60_gt_ema120, avoid_chase, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="2" t="n">
-        <v>6189</v>
+        <v>6257</v>
       </c>
       <c r="B83" s="2" t="inlineStr">
         <is>
-          <t>豐藝</t>
+          <t>矽格</t>
         </is>
       </c>
       <c r="C83" s="2" t="n">
         <v/>
       </c>
       <c r="D83" s="2" t="n">
-        <v>272.4757254108907</v>
+        <v>273.502986139914</v>
       </c>
       <c r="E83" s="2" t="n">
-        <v>49.45</v>
+        <v>197.5</v>
       </c>
       <c r="F83" s="2" t="inlineStr">
         <is>
@@ -4845,13 +4845,13 @@
         <v>0</v>
       </c>
       <c r="H83" s="2" t="n">
-        <v>53.96381867815364</v>
+        <v>42.93069144705502</v>
       </c>
       <c r="I83" s="2" t="n">
-        <v>10.03417744911798</v>
+        <v>14.35913194971289</v>
       </c>
       <c r="J83" s="2" t="n">
-        <v>1.163289062586796</v>
+        <v>0.4136491083731533</v>
       </c>
       <c r="K83" s="2" t="n">
         <v>0</v>
@@ -4863,31 +4863,31 @@
         <v>-1</v>
       </c>
       <c r="N83" s="2" t="n">
-        <v>0.133621385258608</v>
+        <v>0.294254828683421</v>
       </c>
       <c r="O83" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="2" t="n">
-        <v>6197</v>
+        <v>6189</v>
       </c>
       <c r="B84" s="2" t="inlineStr">
         <is>
-          <t>佳必琪</t>
+          <t>豐藝</t>
         </is>
       </c>
       <c r="C84" s="2" t="n">
         <v/>
       </c>
       <c r="D84" s="2" t="n">
-        <v>271.4724233515853</v>
+        <v>272.4757254108907</v>
       </c>
       <c r="E84" s="2" t="n">
-        <v>290</v>
+        <v>49.45</v>
       </c>
       <c r="F84" s="2" t="inlineStr">
         <is>
@@ -4898,13 +4898,13 @@
         <v>0</v>
       </c>
       <c r="H84" s="2" t="n">
-        <v>42.87208886183654</v>
+        <v>53.96381867815364</v>
       </c>
       <c r="I84" s="2" t="n">
-        <v>17.01400682056973</v>
+        <v>10.03417744911798</v>
       </c>
       <c r="J84" s="2" t="n">
-        <v>0.2265139385277157</v>
+        <v>1.163289062586796</v>
       </c>
       <c r="K84" s="2" t="n">
         <v>0</v>
@@ -4916,31 +4916,31 @@
         <v>-1</v>
       </c>
       <c r="N84" s="2" t="n">
-        <v>-0.4141837323718942</v>
+        <v>0.133621385258608</v>
       </c>
       <c r="O84" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok</t>
+          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="2" t="n">
-        <v>6438</v>
+        <v>6197</v>
       </c>
       <c r="B85" s="2" t="inlineStr">
         <is>
-          <t>迅得</t>
+          <t>佳必琪</t>
         </is>
       </c>
       <c r="C85" s="2" t="n">
         <v/>
       </c>
       <c r="D85" s="2" t="n">
-        <v>271.4689188380651</v>
+        <v>271.4724233515853</v>
       </c>
       <c r="E85" s="2" t="n">
-        <v>143.5</v>
+        <v>290</v>
       </c>
       <c r="F85" s="2" t="inlineStr">
         <is>
@@ -4951,13 +4951,13 @@
         <v>0</v>
       </c>
       <c r="H85" s="2" t="n">
-        <v>47.42482002328335</v>
+        <v>42.87208886183654</v>
       </c>
       <c r="I85" s="2" t="n">
-        <v>15.99450892613776</v>
+        <v>17.01400682056973</v>
       </c>
       <c r="J85" s="2" t="n">
-        <v>0.5162539141765212</v>
+        <v>0.2265139385277157</v>
       </c>
       <c r="K85" s="2" t="n">
         <v>0</v>
@@ -4969,31 +4969,31 @@
         <v>-1</v>
       </c>
       <c r="N85" s="2" t="n">
-        <v>0.3630768247823304</v>
+        <v>-0.4141837323718942</v>
       </c>
       <c r="O85" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="2" t="n">
-        <v>6274</v>
+        <v>6438</v>
       </c>
       <c r="B86" s="2" t="inlineStr">
         <is>
-          <t>台燿</t>
+          <t>迅得</t>
         </is>
       </c>
       <c r="C86" s="2" t="n">
         <v/>
       </c>
       <c r="D86" s="2" t="n">
-        <v>271.1505608390356</v>
+        <v>271.4689188380651</v>
       </c>
       <c r="E86" s="2" t="n">
-        <v>1455</v>
+        <v>143.5</v>
       </c>
       <c r="F86" s="2" t="inlineStr">
         <is>
@@ -5004,13 +5004,13 @@
         <v>0</v>
       </c>
       <c r="H86" s="2" t="n">
-        <v>49.4051974791669</v>
+        <v>47.42482002328335</v>
       </c>
       <c r="I86" s="2" t="n">
-        <v>12.49514703155399</v>
+        <v>15.99450892613776</v>
       </c>
       <c r="J86" s="2" t="n">
-        <v>0.6435931528454669</v>
+        <v>0.5162539141765212</v>
       </c>
       <c r="K86" s="2" t="n">
         <v>0</v>
@@ -5022,31 +5022,31 @@
         <v>-1</v>
       </c>
       <c r="N86" s="2" t="n">
-        <v>5.152895164453241</v>
+        <v>0.3630768247823304</v>
       </c>
       <c r="O86" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok</t>
+          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="2" t="n">
-        <v>6282</v>
+        <v>6274</v>
       </c>
       <c r="B87" s="2" t="inlineStr">
         <is>
-          <t>康舒</t>
+          <t>台燿</t>
         </is>
       </c>
       <c r="C87" s="2" t="n">
         <v/>
       </c>
       <c r="D87" s="2" t="n">
-        <v>269.648294277914</v>
+        <v>271.1505608390356</v>
       </c>
       <c r="E87" s="2" t="n">
-        <v>44.35</v>
+        <v>1455</v>
       </c>
       <c r="F87" s="2" t="inlineStr">
         <is>
@@ -5057,13 +5057,13 @@
         <v>0</v>
       </c>
       <c r="H87" s="2" t="n">
-        <v>39.89974676396358</v>
+        <v>49.4051974791669</v>
       </c>
       <c r="I87" s="2" t="n">
-        <v>17.47583666550912</v>
+        <v>12.49514703155399</v>
       </c>
       <c r="J87" s="2" t="n">
-        <v>0.5025718184809561</v>
+        <v>0.6435931528454669</v>
       </c>
       <c r="K87" s="2" t="n">
         <v>0</v>
@@ -5075,7 +5075,7 @@
         <v>-1</v>
       </c>
       <c r="N87" s="2" t="n">
-        <v>0.0442823103008511</v>
+        <v>5.152895164453241</v>
       </c>
       <c r="O87" s="2" t="inlineStr">
         <is>
@@ -5085,21 +5085,21 @@
     </row>
     <row r="88">
       <c r="A88" s="2" t="n">
-        <v>6170</v>
+        <v>6282</v>
       </c>
       <c r="B88" s="2" t="inlineStr">
         <is>
-          <t>統振</t>
+          <t>康舒</t>
         </is>
       </c>
       <c r="C88" s="2" t="n">
         <v/>
       </c>
       <c r="D88" s="2" t="n">
-        <v>266.4484030369605</v>
+        <v>269.648294277914</v>
       </c>
       <c r="E88" s="2" t="n">
-        <v>47.65</v>
+        <v>44.35</v>
       </c>
       <c r="F88" s="2" t="inlineStr">
         <is>
@@ -5110,13 +5110,13 @@
         <v>0</v>
       </c>
       <c r="H88" s="2" t="n">
-        <v>51.54280916384291</v>
+        <v>39.89974676396358</v>
       </c>
       <c r="I88" s="2" t="n">
-        <v>21.48363321374109</v>
+        <v>17.47583666550912</v>
       </c>
       <c r="J88" s="2" t="n">
-        <v>0.3726538442719598</v>
+        <v>0.5025718184809561</v>
       </c>
       <c r="K88" s="2" t="n">
         <v>0</v>
@@ -5128,31 +5128,31 @@
         <v>-1</v>
       </c>
       <c r="N88" s="2" t="n">
-        <v>0.2565330413311399</v>
+        <v>0.0442823103008511</v>
       </c>
       <c r="O88" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="2" t="n">
-        <v>6166</v>
+        <v>6170</v>
       </c>
       <c r="B89" s="2" t="inlineStr">
         <is>
-          <t>凌華</t>
+          <t>統振</t>
         </is>
       </c>
       <c r="C89" s="2" t="n">
         <v/>
       </c>
       <c r="D89" s="2" t="n">
-        <v>264.4507059031736</v>
+        <v>266.4484030369605</v>
       </c>
       <c r="E89" s="2" t="n">
-        <v>119</v>
+        <v>47.65</v>
       </c>
       <c r="F89" s="2" t="inlineStr">
         <is>
@@ -5163,13 +5163,13 @@
         <v>0</v>
       </c>
       <c r="H89" s="2" t="n">
-        <v>40.64049756822645</v>
+        <v>51.54280916384291</v>
       </c>
       <c r="I89" s="2" t="n">
-        <v>14.55166429840185</v>
+        <v>21.48363321374109</v>
       </c>
       <c r="J89" s="2" t="n">
-        <v>0.177116334990296</v>
+        <v>0.3726538442719598</v>
       </c>
       <c r="K89" s="2" t="n">
         <v>0</v>
@@ -5181,31 +5181,31 @@
         <v>-1</v>
       </c>
       <c r="N89" s="2" t="n">
-        <v>-2.017545711469608</v>
+        <v>0.2565330413311399</v>
       </c>
       <c r="O89" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="2" t="n">
-        <v>6222</v>
+        <v>6166</v>
       </c>
       <c r="B90" s="2" t="inlineStr">
         <is>
-          <t>立軒</t>
+          <t>凌華</t>
         </is>
       </c>
       <c r="C90" s="2" t="n">
         <v/>
       </c>
       <c r="D90" s="2" t="n">
-        <v>261.6299693120745</v>
+        <v>264.4507059031736</v>
       </c>
       <c r="E90" s="2" t="n">
-        <v>20.15</v>
+        <v>119</v>
       </c>
       <c r="F90" s="2" t="inlineStr">
         <is>
@@ -5216,13 +5216,13 @@
         <v>0</v>
       </c>
       <c r="H90" s="2" t="n">
-        <v>51.50815291310855</v>
+        <v>40.64049756822645</v>
       </c>
       <c r="I90" s="2" t="n">
-        <v>11.21980345759073</v>
+        <v>14.55166429840185</v>
       </c>
       <c r="J90" s="2" t="n">
-        <v>0.0980796775994756</v>
+        <v>0.177116334990296</v>
       </c>
       <c r="K90" s="2" t="n">
         <v>0</v>
@@ -5234,31 +5234,31 @@
         <v>-1</v>
       </c>
       <c r="N90" s="2" t="n">
-        <v>0.1025280470753168</v>
+        <v>-2.017545711469608</v>
       </c>
       <c r="O90" s="2" t="inlineStr">
         <is>
-          <t>macd_golden_cross, market_above_ma60, avoid_chase, hist_turn_positive, obv_uptrend</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="2" t="n">
-        <v>6165</v>
+        <v>6222</v>
       </c>
       <c r="B91" s="2" t="inlineStr">
         <is>
-          <t>浪凡</t>
+          <t>立軒</t>
         </is>
       </c>
       <c r="C91" s="2" t="n">
         <v/>
       </c>
       <c r="D91" s="2" t="n">
-        <v>260.0416616798924</v>
+        <v>261.6299693120745</v>
       </c>
       <c r="E91" s="2" t="n">
-        <v>47.85</v>
+        <v>20.15</v>
       </c>
       <c r="F91" s="2" t="inlineStr">
         <is>
@@ -5269,13 +5269,13 @@
         <v>0</v>
       </c>
       <c r="H91" s="2" t="n">
-        <v>44.93580469751337</v>
+        <v>51.50815291310855</v>
       </c>
       <c r="I91" s="2" t="n">
-        <v>11.66580533376109</v>
+        <v>11.21980345759073</v>
       </c>
       <c r="J91" s="2" t="n">
-        <v>0.245520317623703</v>
+        <v>0.0980796775994756</v>
       </c>
       <c r="K91" s="2" t="n">
         <v>0</v>
@@ -5287,31 +5287,31 @@
         <v>-1</v>
       </c>
       <c r="N91" s="2" t="n">
-        <v>-0.1894395529647997</v>
+        <v>0.1025280470753168</v>
       </c>
       <c r="O91" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, obv_uptrend</t>
+          <t>macd_golden_cross, market_above_ma60, avoid_chase, hist_turn_positive, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="2" t="n">
-        <v>6285</v>
+        <v>6165</v>
       </c>
       <c r="B92" s="2" t="inlineStr">
         <is>
-          <t>啟碁</t>
+          <t>浪凡</t>
         </is>
       </c>
       <c r="C92" s="2" t="n">
         <v/>
       </c>
       <c r="D92" s="2" t="n">
-        <v>257.9294789755478</v>
+        <v>260.0416616798924</v>
       </c>
       <c r="E92" s="2" t="n">
-        <v>230.5</v>
+        <v>47.85</v>
       </c>
       <c r="F92" s="2" t="inlineStr">
         <is>
@@ -5322,13 +5322,13 @@
         <v>0</v>
       </c>
       <c r="H92" s="2" t="n">
-        <v>43.29158473473947</v>
+        <v>44.93580469751337</v>
       </c>
       <c r="I92" s="2" t="n">
-        <v>16.76029578105354</v>
+        <v>11.66580533376109</v>
       </c>
       <c r="J92" s="2" t="n">
-        <v>0.3303314536139159</v>
+        <v>0.245520317623703</v>
       </c>
       <c r="K92" s="2" t="n">
         <v>0</v>
@@ -5340,31 +5340,31 @@
         <v>-1</v>
       </c>
       <c r="N92" s="2" t="n">
-        <v>-0.7873716264220043</v>
+        <v>-0.1894395529647997</v>
       </c>
       <c r="O92" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="2" t="n">
-        <v>6194</v>
+        <v>6285</v>
       </c>
       <c r="B93" s="2" t="inlineStr">
         <is>
-          <t>育富</t>
+          <t>啟碁</t>
         </is>
       </c>
       <c r="C93" s="2" t="n">
         <v/>
       </c>
       <c r="D93" s="2" t="n">
-        <v>253.6494523137821</v>
+        <v>257.9294789755478</v>
       </c>
       <c r="E93" s="2" t="n">
-        <v>29.45</v>
+        <v>230.5</v>
       </c>
       <c r="F93" s="2" t="inlineStr">
         <is>
@@ -5375,13 +5375,13 @@
         <v>0</v>
       </c>
       <c r="H93" s="2" t="n">
-        <v>35.7952664914153</v>
+        <v>43.29158473473947</v>
       </c>
       <c r="I93" s="2" t="n">
-        <v>26.91459753595431</v>
+        <v>16.76029578105354</v>
       </c>
       <c r="J93" s="2" t="n">
-        <v>0.1389874302415469</v>
+        <v>0.3303314536139159</v>
       </c>
       <c r="K93" s="2" t="n">
         <v>0</v>
@@ -5393,31 +5393,31 @@
         <v>-1</v>
       </c>
       <c r="N93" s="2" t="n">
-        <v>0.0597216100766079</v>
+        <v>-0.7873716264220043</v>
       </c>
       <c r="O93" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="2" t="n">
-        <v>6220</v>
+        <v>6194</v>
       </c>
       <c r="B94" s="2" t="inlineStr">
         <is>
-          <t>岳豐</t>
+          <t>育富</t>
         </is>
       </c>
       <c r="C94" s="2" t="n">
         <v/>
       </c>
       <c r="D94" s="2" t="n">
-        <v>244.9145453838939</v>
+        <v>253.6494523137821</v>
       </c>
       <c r="E94" s="2" t="n">
-        <v>25.6</v>
+        <v>29.45</v>
       </c>
       <c r="F94" s="2" t="inlineStr">
         <is>
@@ -5428,13 +5428,13 @@
         <v>0</v>
       </c>
       <c r="H94" s="2" t="n">
-        <v>38.83869626715457</v>
+        <v>35.7952664914153</v>
       </c>
       <c r="I94" s="2" t="n">
-        <v>26.56225951898541</v>
+        <v>26.91459753595431</v>
       </c>
       <c r="J94" s="2" t="n">
-        <v>0.6286049292212579</v>
+        <v>0.1389874302415469</v>
       </c>
       <c r="K94" s="2" t="n">
         <v>0</v>
@@ -5446,31 +5446,31 @@
         <v>-1</v>
       </c>
       <c r="N94" s="2" t="n">
-        <v>0.2894040068354544</v>
+        <v>0.0597216100766079</v>
       </c>
       <c r="O94" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="2" t="n">
-        <v>6237</v>
+        <v>6220</v>
       </c>
       <c r="B95" s="2" t="inlineStr">
         <is>
-          <t>驊訊</t>
+          <t>岳豐</t>
         </is>
       </c>
       <c r="C95" s="2" t="n">
         <v/>
       </c>
       <c r="D95" s="2" t="n">
-        <v>243.0536392391024</v>
+        <v>244.9145453838939</v>
       </c>
       <c r="E95" s="2" t="n">
-        <v>33.5</v>
+        <v>25.6</v>
       </c>
       <c r="F95" s="2" t="inlineStr">
         <is>
@@ -5481,13 +5481,13 @@
         <v>0</v>
       </c>
       <c r="H95" s="2" t="n">
-        <v>40.64675302367685</v>
+        <v>38.83869626715457</v>
       </c>
       <c r="I95" s="2" t="n">
-        <v>26.76175932662031</v>
+        <v>26.56225951898541</v>
       </c>
       <c r="J95" s="2" t="n">
-        <v>0.4048854441700025</v>
+        <v>0.6286049292212579</v>
       </c>
       <c r="K95" s="2" t="n">
         <v>0</v>
@@ -5499,7 +5499,7 @@
         <v>-1</v>
       </c>
       <c r="N95" s="2" t="n">
-        <v>0.3549576979920579</v>
+        <v>0.2894040068354544</v>
       </c>
       <c r="O95" s="2" t="inlineStr">
         <is>
@@ -5509,21 +5509,21 @@
     </row>
     <row r="96">
       <c r="A96" s="2" t="n">
-        <v>6223</v>
+        <v>6237</v>
       </c>
       <c r="B96" s="2" t="inlineStr">
         <is>
-          <t>旺矽</t>
+          <t>驊訊</t>
         </is>
       </c>
       <c r="C96" s="2" t="n">
         <v/>
       </c>
       <c r="D96" s="2" t="n">
-        <v>242.4844767799632</v>
+        <v>243.0536392391024</v>
       </c>
       <c r="E96" s="2" t="n">
-        <v>5565</v>
+        <v>33.5</v>
       </c>
       <c r="F96" s="2" t="inlineStr">
         <is>
@@ -5534,13 +5534,13 @@
         <v>0</v>
       </c>
       <c r="H96" s="2" t="n">
-        <v>45.27491680385533</v>
+        <v>40.64675302367685</v>
       </c>
       <c r="I96" s="2" t="n">
-        <v>14.67171870669846</v>
+        <v>26.76175932662031</v>
       </c>
       <c r="J96" s="2" t="n">
-        <v>0.6083952331558335</v>
+        <v>0.4048854441700025</v>
       </c>
       <c r="K96" s="2" t="n">
         <v>0</v>
@@ -5552,31 +5552,31 @@
         <v>-1</v>
       </c>
       <c r="N96" s="2" t="n">
-        <v>-56.73116043888743</v>
+        <v>0.3549576979920579</v>
       </c>
       <c r="O96" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok</t>
+          <t>market_above_ma60, avoid_chase, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="2" t="n">
-        <v>6451</v>
+        <v>6223</v>
       </c>
       <c r="B97" s="2" t="inlineStr">
         <is>
-          <t>訊芯-KY</t>
+          <t>旺矽</t>
         </is>
       </c>
       <c r="C97" s="2" t="n">
         <v/>
       </c>
       <c r="D97" s="2" t="n">
-        <v>237.3206143842549</v>
+        <v>242.4844767799632</v>
       </c>
       <c r="E97" s="2" t="n">
-        <v>400</v>
+        <v>5565</v>
       </c>
       <c r="F97" s="2" t="inlineStr">
         <is>
@@ -5587,13 +5587,13 @@
         <v>0</v>
       </c>
       <c r="H97" s="2" t="n">
-        <v>44.36010370642237</v>
+        <v>45.27491680385533</v>
       </c>
       <c r="I97" s="2" t="n">
-        <v>12.0042981159281</v>
+        <v>14.67171870669846</v>
       </c>
       <c r="J97" s="2" t="n">
-        <v>0.6848481276198697</v>
+        <v>0.6083952331558335</v>
       </c>
       <c r="K97" s="2" t="n">
         <v>0</v>
@@ -5605,7 +5605,7 @@
         <v>-1</v>
       </c>
       <c r="N97" s="2" t="n">
-        <v>2.699133725127954</v>
+        <v>-56.73116043888743</v>
       </c>
       <c r="O97" s="2" t="inlineStr">
         <is>
@@ -5615,21 +5615,21 @@
     </row>
     <row r="98">
       <c r="A98" s="2" t="n">
-        <v>6229</v>
+        <v>6451</v>
       </c>
       <c r="B98" s="2" t="inlineStr">
         <is>
-          <t>研通</t>
+          <t>訊芯-KY</t>
         </is>
       </c>
       <c r="C98" s="2" t="n">
         <v/>
       </c>
       <c r="D98" s="2" t="n">
-        <v>232.0198060033378</v>
+        <v>237.3206143842549</v>
       </c>
       <c r="E98" s="2" t="n">
-        <v>23.3</v>
+        <v>400</v>
       </c>
       <c r="F98" s="2" t="inlineStr">
         <is>
@@ -5640,13 +5640,13 @@
         <v>0</v>
       </c>
       <c r="H98" s="2" t="n">
-        <v>42.3160579030604</v>
+        <v>44.36010370642237</v>
       </c>
       <c r="I98" s="2" t="n">
-        <v>16.1924942866129</v>
+        <v>12.0042981159281</v>
       </c>
       <c r="J98" s="2" t="n">
-        <v>0.6536228422154073</v>
+        <v>0.6848481276198697</v>
       </c>
       <c r="K98" s="2" t="n">
         <v>0</v>
@@ -5658,31 +5658,31 @@
         <v>-1</v>
       </c>
       <c r="N98" s="2" t="n">
-        <v>0.0881618123908251</v>
+        <v>2.699133725127954</v>
       </c>
       <c r="O98" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, obv_uptrend</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="2" t="n">
-        <v>6443</v>
+        <v>6229</v>
       </c>
       <c r="B99" s="2" t="inlineStr">
         <is>
-          <t>元晶</t>
+          <t>研通</t>
         </is>
       </c>
       <c r="C99" s="2" t="n">
         <v/>
       </c>
       <c r="D99" s="2" t="n">
-        <v>230.6579919034105</v>
+        <v>232.0198060033378</v>
       </c>
       <c r="E99" s="2" t="n">
-        <v>25.85</v>
+        <v>23.3</v>
       </c>
       <c r="F99" s="2" t="inlineStr">
         <is>
@@ -5693,13 +5693,13 @@
         <v>0</v>
       </c>
       <c r="H99" s="2" t="n">
-        <v>41.10029652055359</v>
+        <v>42.3160579030604</v>
       </c>
       <c r="I99" s="2" t="n">
-        <v>16.31418728095099</v>
+        <v>16.1924942866129</v>
       </c>
       <c r="J99" s="2" t="n">
-        <v>0.614365406012233</v>
+        <v>0.6536228422154073</v>
       </c>
       <c r="K99" s="2" t="n">
         <v>0</v>
@@ -5711,31 +5711,31 @@
         <v>-1</v>
       </c>
       <c r="N99" s="2" t="n">
-        <v>0.2619159081625741</v>
+        <v>0.0881618123908251</v>
       </c>
       <c r="O99" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="2" t="n">
-        <v>6184</v>
+        <v>6443</v>
       </c>
       <c r="B100" s="2" t="inlineStr">
         <is>
-          <t>大豐電</t>
+          <t>元晶</t>
         </is>
       </c>
       <c r="C100" s="2" t="n">
         <v/>
       </c>
       <c r="D100" s="2" t="n">
-        <v>226.085250171077</v>
+        <v>230.6579919034105</v>
       </c>
       <c r="E100" s="2" t="n">
-        <v>41.6</v>
+        <v>25.85</v>
       </c>
       <c r="F100" s="2" t="inlineStr">
         <is>
@@ -5746,13 +5746,13 @@
         <v>0</v>
       </c>
       <c r="H100" s="2" t="n">
-        <v>26.73192882003428</v>
+        <v>41.10029652055359</v>
       </c>
       <c r="I100" s="2" t="n">
-        <v>18.86879287512037</v>
+        <v>16.31418728095099</v>
       </c>
       <c r="J100" s="2" t="n">
-        <v>1.079072356860766</v>
+        <v>0.614365406012233</v>
       </c>
       <c r="K100" s="2" t="n">
         <v>0</v>
@@ -5764,31 +5764,31 @@
         <v>-1</v>
       </c>
       <c r="N100" s="2" t="n">
-        <v>0.0106105442620531</v>
+        <v>0.2619159081625741</v>
       </c>
       <c r="O100" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, kd_golden_cross</t>
+          <t>market_above_ma60, avoid_chase, liquidity_ok, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="2" t="n">
-        <v>6246</v>
+        <v>6184</v>
       </c>
       <c r="B101" s="2" t="inlineStr">
         <is>
-          <t>臺龍</t>
+          <t>大豐電</t>
         </is>
       </c>
       <c r="C101" s="2" t="n">
         <v/>
       </c>
       <c r="D101" s="2" t="n">
-        <v>222.6280885010653</v>
+        <v>226.085250171077</v>
       </c>
       <c r="E101" s="2" t="n">
-        <v>12.4</v>
+        <v>41.6</v>
       </c>
       <c r="F101" s="2" t="inlineStr">
         <is>
@@ -5799,13 +5799,13 @@
         <v>0</v>
       </c>
       <c r="H101" s="2" t="n">
-        <v>42.13353346672421</v>
+        <v>26.73192882003428</v>
       </c>
       <c r="I101" s="2" t="n">
-        <v>20.66588562644485</v>
+        <v>18.86879287512037</v>
       </c>
       <c r="J101" s="2" t="n">
-        <v>0.1594958580505381</v>
+        <v>1.079072356860766</v>
       </c>
       <c r="K101" s="2" t="n">
         <v>0</v>
@@ -5817,31 +5817,31 @@
         <v>-1</v>
       </c>
       <c r="N101" s="2" t="n">
-        <v>0.091646049421873</v>
+        <v>0.0106105442620531</v>
       </c>
       <c r="O101" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="2" t="n">
-        <v>6412</v>
+        <v>6246</v>
       </c>
       <c r="B102" s="2" t="inlineStr">
         <is>
-          <t>群電</t>
+          <t>臺龍</t>
         </is>
       </c>
       <c r="C102" s="2" t="n">
         <v/>
       </c>
       <c r="D102" s="2" t="n">
-        <v>221.5045329116221</v>
+        <v>222.6280885010653</v>
       </c>
       <c r="E102" s="2" t="n">
-        <v>77.7</v>
+        <v>12.4</v>
       </c>
       <c r="F102" s="2" t="inlineStr">
         <is>
@@ -5852,13 +5852,13 @@
         <v>0</v>
       </c>
       <c r="H102" s="2" t="n">
-        <v>41.4896665736444</v>
+        <v>42.13353346672421</v>
       </c>
       <c r="I102" s="2" t="n">
-        <v>27.66198614268608</v>
+        <v>20.66588562644485</v>
       </c>
       <c r="J102" s="2" t="n">
-        <v>0.2523750671596922</v>
+        <v>0.1594958580505381</v>
       </c>
       <c r="K102" s="2" t="n">
         <v>0</v>
@@ -5870,31 +5870,31 @@
         <v>-1</v>
       </c>
       <c r="N102" s="2" t="n">
-        <v>0.3299517163702807</v>
+        <v>0.091646049421873</v>
       </c>
       <c r="O102" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok, adx_trending</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="2" t="n">
-        <v>6205</v>
+        <v>6412</v>
       </c>
       <c r="B103" s="2" t="inlineStr">
         <is>
-          <t>詮欣</t>
+          <t>群電</t>
         </is>
       </c>
       <c r="C103" s="2" t="n">
         <v/>
       </c>
       <c r="D103" s="2" t="n">
-        <v>212.0954517308882</v>
+        <v>221.5045329116221</v>
       </c>
       <c r="E103" s="2" t="n">
-        <v>59.8</v>
+        <v>77.7</v>
       </c>
       <c r="F103" s="2" t="inlineStr">
         <is>
@@ -5905,13 +5905,13 @@
         <v>0</v>
       </c>
       <c r="H103" s="2" t="n">
-        <v>42.43698642815235</v>
+        <v>41.4896665736444</v>
       </c>
       <c r="I103" s="2" t="n">
-        <v>16.69403343188486</v>
+        <v>27.66198614268608</v>
       </c>
       <c r="J103" s="2" t="n">
-        <v>0.2943081369801872</v>
+        <v>0.2523750671596922</v>
       </c>
       <c r="K103" s="2" t="n">
         <v>0</v>
@@ -5923,31 +5923,31 @@
         <v>-1</v>
       </c>
       <c r="N103" s="2" t="n">
-        <v>0.5260814420233533</v>
+        <v>0.3299517163702807</v>
       </c>
       <c r="O103" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase</t>
+          <t>market_above_ma60, avoid_chase, liquidity_ok, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="2" t="n">
-        <v>6462</v>
+        <v>6205</v>
       </c>
       <c r="B104" s="2" t="inlineStr">
         <is>
-          <t>神盾</t>
+          <t>詮欣</t>
         </is>
       </c>
       <c r="C104" s="2" t="n">
         <v/>
       </c>
       <c r="D104" s="2" t="n">
-        <v>209.5005174784779</v>
+        <v>212.0954517308882</v>
       </c>
       <c r="E104" s="2" t="n">
-        <v>98.90000000000001</v>
+        <v>59.8</v>
       </c>
       <c r="F104" s="2" t="inlineStr">
         <is>
@@ -5958,13 +5958,13 @@
         <v>0</v>
       </c>
       <c r="H104" s="2" t="n">
-        <v>45.92095627605833</v>
+        <v>42.43698642815235</v>
       </c>
       <c r="I104" s="2" t="n">
-        <v>13.99527690194889</v>
+        <v>16.69403343188486</v>
       </c>
       <c r="J104" s="2" t="n">
-        <v>1.050113340146162</v>
+        <v>0.2943081369801872</v>
       </c>
       <c r="K104" s="2" t="n">
         <v>0</v>
@@ -5976,31 +5976,31 @@
         <v>-1</v>
       </c>
       <c r="N104" s="2" t="n">
-        <v>0.6140850450746056</v>
+        <v>0.5260814420233533</v>
       </c>
       <c r="O104" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="2" t="n">
-        <v>6236</v>
+        <v>6462</v>
       </c>
       <c r="B105" s="2" t="inlineStr">
         <is>
-          <t>中湛</t>
+          <t>神盾</t>
         </is>
       </c>
       <c r="C105" s="2" t="n">
         <v/>
       </c>
       <c r="D105" s="2" t="n">
-        <v>209.2771474433183</v>
+        <v>209.5005174784779</v>
       </c>
       <c r="E105" s="2" t="n">
-        <v>0</v>
+        <v>98.90000000000001</v>
       </c>
       <c r="F105" s="2" t="inlineStr">
         <is>
@@ -6011,13 +6011,13 @@
         <v>0</v>
       </c>
       <c r="H105" s="2" t="n">
-        <v>47.71440566745167</v>
+        <v>45.92095627605833</v>
       </c>
       <c r="I105" s="2" t="n">
-        <v>9.864081740330541</v>
+        <v>13.99527690194889</v>
       </c>
       <c r="J105" s="2" t="n">
-        <v>0</v>
+        <v>1.050113340146162</v>
       </c>
       <c r="K105" s="2" t="n">
         <v>0</v>
@@ -6029,31 +6029,31 @@
         <v>-1</v>
       </c>
       <c r="N105" s="2" t="n">
-        <v>0.0899415674148393</v>
+        <v>0.6140850450746056</v>
       </c>
       <c r="O105" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, obv_uptrend, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="2" t="n">
-        <v>6272</v>
+        <v>6236</v>
       </c>
       <c r="B106" s="2" t="inlineStr">
         <is>
-          <t>驊陞</t>
+          <t>中湛</t>
         </is>
       </c>
       <c r="C106" s="2" t="n">
         <v/>
       </c>
       <c r="D106" s="2" t="n">
-        <v>196.1821775036049</v>
+        <v>209.2771474433183</v>
       </c>
       <c r="E106" s="2" t="n">
-        <v>23.25</v>
+        <v>0</v>
       </c>
       <c r="F106" s="2" t="inlineStr">
         <is>
@@ -6064,13 +6064,13 @@
         <v>0</v>
       </c>
       <c r="H106" s="2" t="n">
-        <v>35.54639560599293</v>
+        <v>47.71440566745167</v>
       </c>
       <c r="I106" s="2" t="n">
-        <v>44.11938359217351</v>
+        <v>9.864081740330541</v>
       </c>
       <c r="J106" s="2" t="n">
-        <v>0.4984345695180321</v>
+        <v>0</v>
       </c>
       <c r="K106" s="2" t="n">
         <v>0</v>
@@ -6082,31 +6082,31 @@
         <v>-1</v>
       </c>
       <c r="N106" s="2" t="n">
-        <v>0.1611554177983212</v>
+        <v>0.0899415674148393</v>
       </c>
       <c r="O106" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending</t>
+          <t>market_above_ma60, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="2" t="n">
-        <v>6283</v>
+        <v>6272</v>
       </c>
       <c r="B107" s="2" t="inlineStr">
         <is>
-          <t>淳安</t>
+          <t>驊陞</t>
         </is>
       </c>
       <c r="C107" s="2" t="n">
         <v/>
       </c>
       <c r="D107" s="2" t="n">
-        <v>193.9267145944455</v>
+        <v>196.1821775036049</v>
       </c>
       <c r="E107" s="2" t="n">
-        <v>20.1</v>
+        <v>23.25</v>
       </c>
       <c r="F107" s="2" t="inlineStr">
         <is>
@@ -6117,13 +6117,13 @@
         <v>0</v>
       </c>
       <c r="H107" s="2" t="n">
-        <v>40.78869034013211</v>
+        <v>35.54639560599293</v>
       </c>
       <c r="I107" s="2" t="n">
-        <v>36.60209457775721</v>
+        <v>44.11938359217351</v>
       </c>
       <c r="J107" s="2" t="n">
-        <v>0.4617021367503108</v>
+        <v>0.4984345695180321</v>
       </c>
       <c r="K107" s="2" t="n">
         <v>0</v>
@@ -6135,7 +6135,7 @@
         <v>-1</v>
       </c>
       <c r="N107" s="2" t="n">
-        <v>0.1184681441087125</v>
+        <v>0.1611554177983212</v>
       </c>
       <c r="O107" s="2" t="inlineStr">
         <is>
@@ -6145,21 +6145,21 @@
     </row>
     <row r="108">
       <c r="A108" s="2" t="n">
-        <v>6188</v>
+        <v>6283</v>
       </c>
       <c r="B108" s="2" t="inlineStr">
         <is>
-          <t>廣明</t>
+          <t>淳安</t>
         </is>
       </c>
       <c r="C108" s="2" t="n">
         <v/>
       </c>
       <c r="D108" s="2" t="n">
-        <v>188.0188464995563</v>
+        <v>193.9267145944455</v>
       </c>
       <c r="E108" s="2" t="n">
-        <v>67.5</v>
+        <v>20.1</v>
       </c>
       <c r="F108" s="2" t="inlineStr">
         <is>
@@ -6170,13 +6170,13 @@
         <v>0</v>
       </c>
       <c r="H108" s="2" t="n">
-        <v>37.28233427451851</v>
+        <v>40.78869034013211</v>
       </c>
       <c r="I108" s="2" t="n">
-        <v>19.56882920323192</v>
+        <v>36.60209457775721</v>
       </c>
       <c r="J108" s="2" t="n">
-        <v>0.5245058245465721</v>
+        <v>0.4617021367503108</v>
       </c>
       <c r="K108" s="2" t="n">
         <v>0</v>
@@ -6188,31 +6188,31 @@
         <v>-1</v>
       </c>
       <c r="N108" s="2" t="n">
-        <v>-0.0057072567934017</v>
+        <v>0.1184681441087125</v>
       </c>
       <c r="O108" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok</t>
+          <t>market_above_ma60, avoid_chase, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" s="2" t="n">
-        <v>6167</v>
+        <v>6188</v>
       </c>
       <c r="B109" s="2" t="inlineStr">
         <is>
-          <t>久正</t>
+          <t>廣明</t>
         </is>
       </c>
       <c r="C109" s="2" t="n">
         <v/>
       </c>
       <c r="D109" s="2" t="n">
-        <v>177.3338469356699</v>
+        <v>188.0188464995563</v>
       </c>
       <c r="E109" s="2" t="n">
-        <v>10.65</v>
+        <v>67.5</v>
       </c>
       <c r="F109" s="2" t="inlineStr">
         <is>
@@ -6223,13 +6223,13 @@
         <v>0</v>
       </c>
       <c r="H109" s="2" t="n">
-        <v>47.56950579450967</v>
+        <v>37.28233427451851</v>
       </c>
       <c r="I109" s="2" t="n">
-        <v>13.80246405543776</v>
+        <v>19.56882920323192</v>
       </c>
       <c r="J109" s="2" t="n">
-        <v>0.1604529529061541</v>
+        <v>0.5245058245465721</v>
       </c>
       <c r="K109" s="2" t="n">
         <v>0</v>
@@ -6241,31 +6241,31 @@
         <v>-1</v>
       </c>
       <c r="N109" s="2" t="n">
-        <v>0.0788650924041313</v>
+        <v>-0.0057072567934017</v>
       </c>
       <c r="O109" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, obv_uptrend</t>
+          <t>market_above_ma60, avoid_chase, liquidity_ok</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" s="2" t="n">
-        <v>6201</v>
+        <v>6167</v>
       </c>
       <c r="B110" s="2" t="inlineStr">
         <is>
-          <t>亞弘電</t>
+          <t>久正</t>
         </is>
       </c>
       <c r="C110" s="2" t="n">
         <v/>
       </c>
       <c r="D110" s="2" t="n">
-        <v>162.5240451224803</v>
+        <v>177.3338469356699</v>
       </c>
       <c r="E110" s="2" t="n">
-        <v>44.8</v>
+        <v>10.65</v>
       </c>
       <c r="F110" s="2" t="inlineStr">
         <is>
@@ -6276,13 +6276,13 @@
         <v>0</v>
       </c>
       <c r="H110" s="2" t="n">
-        <v>32.57787821268251</v>
+        <v>47.56950579450967</v>
       </c>
       <c r="I110" s="2" t="n">
-        <v>23.73988376386698</v>
+        <v>13.80246405543776</v>
       </c>
       <c r="J110" s="2" t="n">
-        <v>0.4012963600456579</v>
+        <v>0.1604529529061541</v>
       </c>
       <c r="K110" s="2" t="n">
         <v>0</v>
@@ -6294,31 +6294,31 @@
         <v>-1</v>
       </c>
       <c r="N110" s="2" t="n">
-        <v>-0.08404536805429361</v>
+        <v>0.0788650924041313</v>
       </c>
       <c r="O110" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending</t>
+          <t>market_above_ma60, avoid_chase, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" s="2" t="n">
-        <v>6276</v>
+        <v>6201</v>
       </c>
       <c r="B111" s="2" t="inlineStr">
         <is>
-          <t>安鈦克</t>
+          <t>亞弘電</t>
         </is>
       </c>
       <c r="C111" s="2" t="n">
         <v/>
       </c>
       <c r="D111" s="2" t="n">
-        <v>160.7767473321378</v>
+        <v>162.5240451224803</v>
       </c>
       <c r="E111" s="2" t="n">
-        <v>19.85</v>
+        <v>44.8</v>
       </c>
       <c r="F111" s="2" t="inlineStr">
         <is>
@@ -6329,13 +6329,13 @@
         <v>0</v>
       </c>
       <c r="H111" s="2" t="n">
-        <v>45.84813191117963</v>
+        <v>32.57787821268251</v>
       </c>
       <c r="I111" s="2" t="n">
-        <v>25.60001768542313</v>
+        <v>23.73988376386698</v>
       </c>
       <c r="J111" s="2" t="n">
-        <v>0.6741922630603916</v>
+        <v>0.4012963600456579</v>
       </c>
       <c r="K111" s="2" t="n">
         <v>0</v>
@@ -6347,7 +6347,7 @@
         <v>-1</v>
       </c>
       <c r="N111" s="2" t="n">
-        <v>0.1528368231170304</v>
+        <v>-0.08404536805429361</v>
       </c>
       <c r="O111" s="2" t="inlineStr">
         <is>
@@ -6357,21 +6357,21 @@
     </row>
     <row r="112">
       <c r="A112" s="2" t="n">
-        <v>6208</v>
+        <v>6276</v>
       </c>
       <c r="B112" s="2" t="inlineStr">
         <is>
-          <t>日揚</t>
+          <t>安鈦克</t>
         </is>
       </c>
       <c r="C112" s="2" t="n">
         <v/>
       </c>
       <c r="D112" s="2" t="n">
-        <v>159.4319374865121</v>
+        <v>160.7767473321378</v>
       </c>
       <c r="E112" s="2" t="n">
-        <v>81.59999999999999</v>
+        <v>19.85</v>
       </c>
       <c r="F112" s="2" t="inlineStr">
         <is>
@@ -6382,13 +6382,13 @@
         <v>0</v>
       </c>
       <c r="H112" s="2" t="n">
-        <v>44.65814816783412</v>
+        <v>45.84813191117963</v>
       </c>
       <c r="I112" s="2" t="n">
-        <v>9.883482708219001</v>
+        <v>25.60001768542313</v>
       </c>
       <c r="J112" s="2" t="n">
-        <v>0.2906986487604893</v>
+        <v>0.6741922630603916</v>
       </c>
       <c r="K112" s="2" t="n">
         <v>0</v>
@@ -6400,31 +6400,31 @@
         <v>-1</v>
       </c>
       <c r="N112" s="2" t="n">
-        <v>0.342015416114596</v>
+        <v>0.1528368231170304</v>
       </c>
       <c r="O112" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase</t>
+          <t>market_above_ma60, avoid_chase, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" s="2" t="n">
-        <v>6185</v>
+        <v>6208</v>
       </c>
       <c r="B113" s="2" t="inlineStr">
         <is>
-          <t>幃翔</t>
+          <t>日揚</t>
         </is>
       </c>
       <c r="C113" s="2" t="n">
         <v/>
       </c>
       <c r="D113" s="2" t="n">
-        <v>159.3035523088612</v>
+        <v>159.4319374865121</v>
       </c>
       <c r="E113" s="2" t="n">
-        <v>12.85</v>
+        <v>81.59999999999999</v>
       </c>
       <c r="F113" s="2" t="inlineStr">
         <is>
@@ -6435,13 +6435,13 @@
         <v>0</v>
       </c>
       <c r="H113" s="2" t="n">
-        <v>28.08338574071149</v>
+        <v>44.65814816783412</v>
       </c>
       <c r="I113" s="2" t="n">
-        <v>18.68114616177608</v>
+        <v>9.883482708219001</v>
       </c>
       <c r="J113" s="2" t="n">
-        <v>0.830355230886126</v>
+        <v>0.2906986487604893</v>
       </c>
       <c r="K113" s="2" t="n">
         <v>0</v>
@@ -6453,31 +6453,31 @@
         <v>-1</v>
       </c>
       <c r="N113" s="2" t="n">
-        <v>-0.07597568417139169</v>
+        <v>0.342015416114596</v>
       </c>
       <c r="O113" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" s="2" t="n">
-        <v>6210</v>
+        <v>6185</v>
       </c>
       <c r="B114" s="2" t="inlineStr">
         <is>
-          <t>慶生</t>
+          <t>幃翔</t>
         </is>
       </c>
       <c r="C114" s="2" t="n">
         <v/>
       </c>
       <c r="D114" s="2" t="n">
-        <v>133.9546151594086</v>
+        <v>159.3035523088612</v>
       </c>
       <c r="E114" s="2" t="n">
-        <v>17.7</v>
+        <v>12.85</v>
       </c>
       <c r="F114" s="2" t="inlineStr">
         <is>
@@ -6488,13 +6488,13 @@
         <v>0</v>
       </c>
       <c r="H114" s="2" t="n">
-        <v>50.50188752977198</v>
+        <v>28.08338574071149</v>
       </c>
       <c r="I114" s="2" t="n">
-        <v>8.682160984557157</v>
+        <v>18.68114616177608</v>
       </c>
       <c r="J114" s="2" t="n">
-        <v>0.6046459215376938</v>
+        <v>0.830355230886126</v>
       </c>
       <c r="K114" s="2" t="n">
         <v>0</v>
@@ -6506,7 +6506,7 @@
         <v>-1</v>
       </c>
       <c r="N114" s="2" t="n">
-        <v>0.1068093742532773</v>
+        <v>-0.07597568417139169</v>
       </c>
       <c r="O114" s="2" t="inlineStr">
         <is>
@@ -6516,21 +6516,21 @@
     </row>
     <row r="115">
       <c r="A115" s="2" t="n">
-        <v>6235</v>
+        <v>6210</v>
       </c>
       <c r="B115" s="2" t="inlineStr">
         <is>
-          <t>華孚</t>
+          <t>慶生</t>
         </is>
       </c>
       <c r="C115" s="2" t="n">
         <v/>
       </c>
       <c r="D115" s="2" t="n">
-        <v>133.3568492449076</v>
+        <v>133.9546151594086</v>
       </c>
       <c r="E115" s="2" t="n">
-        <v>37.7</v>
+        <v>17.7</v>
       </c>
       <c r="F115" s="2" t="inlineStr">
         <is>
@@ -6541,13 +6541,13 @@
         <v>0</v>
       </c>
       <c r="H115" s="2" t="n">
-        <v>43.22752518786008</v>
+        <v>50.50188752977198</v>
       </c>
       <c r="I115" s="2" t="n">
-        <v>13.00616331553954</v>
+        <v>8.682160984557157</v>
       </c>
       <c r="J115" s="2" t="n">
-        <v>0.4308759147067134</v>
+        <v>0.6046459215376938</v>
       </c>
       <c r="K115" s="2" t="n">
         <v>0</v>
@@ -6559,7 +6559,7 @@
         <v>-1</v>
       </c>
       <c r="N115" s="2" t="n">
-        <v>0.0173625786416331</v>
+        <v>0.1068093742532773</v>
       </c>
       <c r="O115" s="2" t="inlineStr">
         <is>
@@ -6569,21 +6569,21 @@
     </row>
     <row r="116">
       <c r="A116" s="2" t="n">
-        <v>6203</v>
+        <v>6235</v>
       </c>
       <c r="B116" s="2" t="inlineStr">
         <is>
-          <t>海韻電</t>
+          <t>華孚</t>
         </is>
       </c>
       <c r="C116" s="2" t="n">
         <v/>
       </c>
       <c r="D116" s="2" t="n">
-        <v>79.91832896796242</v>
+        <v>133.3568492449076</v>
       </c>
       <c r="E116" s="2" t="n">
-        <v>59.9</v>
+        <v>37.7</v>
       </c>
       <c r="F116" s="2" t="inlineStr">
         <is>
@@ -6594,13 +6594,13 @@
         <v>0</v>
       </c>
       <c r="H116" s="2" t="n">
-        <v>32.16278391556746</v>
+        <v>43.22752518786008</v>
       </c>
       <c r="I116" s="2" t="n">
-        <v>17.72875651380865</v>
+        <v>13.00616331553954</v>
       </c>
       <c r="J116" s="2" t="n">
-        <v>0.6875830920249868</v>
+        <v>0.4308759147067134</v>
       </c>
       <c r="K116" s="2" t="n">
         <v>0</v>
@@ -6612,7 +6612,7 @@
         <v>-1</v>
       </c>
       <c r="N116" s="2" t="n">
-        <v>0.0598823438539857</v>
+        <v>0.0173625786416331</v>
       </c>
       <c r="O116" s="2" t="inlineStr">
         <is>
@@ -6622,52 +6622,105 @@
     </row>
     <row r="117">
       <c r="A117" s="2" t="n">
+        <v>6203</v>
+      </c>
+      <c r="B117" s="2" t="inlineStr">
+        <is>
+          <t>海韻電</t>
+        </is>
+      </c>
+      <c r="C117" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D117" s="2" t="n">
+        <v>79.91832896796242</v>
+      </c>
+      <c r="E117" s="2" t="n">
+        <v>59.9</v>
+      </c>
+      <c r="F117" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="G117" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H117" s="2" t="n">
+        <v>32.16278391556746</v>
+      </c>
+      <c r="I117" s="2" t="n">
+        <v>17.72875651380865</v>
+      </c>
+      <c r="J117" s="2" t="n">
+        <v>0.6875830920249868</v>
+      </c>
+      <c r="K117" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L117" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M117" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N117" s="2" t="n">
+        <v>0.0598823438539857</v>
+      </c>
+      <c r="O117" s="2" t="inlineStr">
+        <is>
+          <t>market_above_ma60, avoid_chase</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="2" t="n">
         <v>6228</v>
       </c>
-      <c r="B117" s="2" t="inlineStr">
+      <c r="B118" s="2" t="inlineStr">
         <is>
           <t>全譜</t>
         </is>
       </c>
-      <c r="C117" s="2" t="n">
-        <v/>
-      </c>
-      <c r="D117" s="2" t="n">
+      <c r="C118" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D118" s="2" t="n">
         <v>65.81858011522336</v>
       </c>
-      <c r="E117" s="2" t="n">
+      <c r="E118" s="2" t="n">
         <v>17.35</v>
       </c>
-      <c r="F117" s="2" t="inlineStr">
-        <is>
-          <t>2026-08-24</t>
-        </is>
-      </c>
-      <c r="G117" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="H117" s="2" t="n">
+      <c r="F118" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="G118" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H118" s="2" t="n">
         <v>51.37904817170691</v>
       </c>
-      <c r="I117" s="2" t="n">
+      <c r="I118" s="2" t="n">
         <v>8.029322890124325</v>
       </c>
-      <c r="J117" s="2" t="n">
+      <c r="J118" s="2" t="n">
         <v>0.7986573405591915</v>
       </c>
-      <c r="K117" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="L117" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="M117" s="2" t="n">
-        <v>-1</v>
-      </c>
-      <c r="N117" s="2" t="n">
+      <c r="K118" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L118" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M118" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N118" s="2" t="n">
         <v>0.6906542476635991</v>
       </c>
-      <c r="O117" s="2" t="inlineStr">
+      <c r="O118" s="2" t="inlineStr">
         <is>
           <t>market_above_ma60</t>
         </is>
